--- a/run-statistics/linear-advection-reaction/linear_adv_rec_stats_fixed.xlsx
+++ b/run-statistics/linear-advection-reaction/linear_adv_rec_stats_fixed.xlsx
@@ -562,46 +562,46 @@
         <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I2" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>400000</v>
+        <v>409602</v>
       </c>
       <c r="L2" t="n">
-        <v>600000</v>
+        <v>614403</v>
       </c>
       <c r="M2" t="n">
-        <v>1000000</v>
+        <v>1024005</v>
       </c>
       <c r="N2" t="n">
-        <v>2.6052e-07</v>
+        <v>2.5363e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.9279e-07</v>
+        <v>1.8653e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>2.6052e-07</v>
+        <v>2.5363e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.9478e-08</v>
+        <v>3.7894e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>3.7267e-08</v>
+        <v>3.5598e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>7.6745e-08</v>
+        <v>7.349100000000001e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>90.56765985488892</v>
+        <v>92.61342811584473</v>
       </c>
     </row>
     <row r="3">
@@ -631,28 +631,28 @@
         <v>0.1</v>
       </c>
       <c r="H3" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I3" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>600000</v>
+        <v>614403</v>
       </c>
       <c r="L3" t="n">
-        <v>800000</v>
+        <v>819204</v>
       </c>
       <c r="M3" t="n">
-        <v>1400000</v>
+        <v>1433607</v>
       </c>
       <c r="N3" t="n">
         <v>1.1395e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>5.6763e-08</v>
+        <v>5.6764e-08</v>
       </c>
       <c r="P3" t="n">
         <v>1.1395e-07</v>
@@ -661,16 +661,16 @@
         <v>1.1162e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>5.5691e-09</v>
+        <v>5.5687e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6732e-08</v>
+        <v>1.6731e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>104.7270803451538</v>
+        <v>107.7226221561432</v>
       </c>
     </row>
     <row r="4">
@@ -700,46 +700,46 @@
         <v>0.1</v>
       </c>
       <c r="H4" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I4" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>600000</v>
+        <v>614403</v>
       </c>
       <c r="L4" t="n">
-        <v>800000</v>
+        <v>819204</v>
       </c>
       <c r="M4" t="n">
-        <v>1400000</v>
+        <v>1433607</v>
       </c>
       <c r="N4" t="n">
-        <v>1.8754e-07</v>
+        <v>1.84e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2621e-07</v>
+        <v>1.2301e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8754e-07</v>
+        <v>1.84e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2989e-08</v>
+        <v>2.2248e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9869e-08</v>
+        <v>1.9061e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2858e-08</v>
+        <v>4.131e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>114.4338319301605</v>
+        <v>117.621691942215</v>
       </c>
     </row>
     <row r="5">
@@ -769,28 +769,28 @@
         <v>0.1</v>
       </c>
       <c r="H5" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I5" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>600000</v>
+        <v>614403</v>
       </c>
       <c r="L5" t="n">
-        <v>800000</v>
+        <v>819204</v>
       </c>
       <c r="M5" t="n">
-        <v>1400000</v>
+        <v>1433607</v>
       </c>
       <c r="N5" t="n">
         <v>1.1409e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>5.6657e-08</v>
+        <v>5.6664e-08</v>
       </c>
       <c r="P5" t="n">
         <v>1.1409e-07</v>
@@ -799,16 +799,16 @@
         <v>1.1162e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>5.5621e-09</v>
+        <v>5.5622e-09</v>
       </c>
       <c r="S5" t="n">
         <v>1.6724e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>83.26296710968018</v>
+        <v>85.56322717666626</v>
       </c>
     </row>
     <row r="6">
@@ -838,46 +838,46 @@
         <v>0.1</v>
       </c>
       <c r="H6" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I6" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>800000</v>
+        <v>819204</v>
       </c>
       <c r="L6" t="n">
-        <v>1800000</v>
+        <v>1843209</v>
       </c>
       <c r="M6" t="n">
-        <v>2600000</v>
+        <v>2662413</v>
       </c>
       <c r="N6" t="n">
         <v>1.1408e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>5.6701e-08</v>
+        <v>5.6706e-08</v>
       </c>
       <c r="P6" t="n">
         <v>1.1408e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.1171e-08</v>
+        <v>1.1164e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.5678e-09</v>
+        <v>5.5646e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.6739e-08</v>
+        <v>1.6729e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>103.3495717048645</v>
+        <v>103.0318551063538</v>
       </c>
     </row>
     <row r="7">
@@ -907,46 +907,46 @@
         <v>0.05</v>
       </c>
       <c r="H7" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I7" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>400000</v>
+        <v>409602</v>
       </c>
       <c r="L7" t="n">
-        <v>600000</v>
+        <v>614403</v>
       </c>
       <c r="M7" t="n">
-        <v>1000000</v>
+        <v>1024005</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1904e-07</v>
+        <v>3.0618e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>3.159e-07</v>
+        <v>3.0279e-07</v>
       </c>
       <c r="P7" t="n">
-        <v>3.1904e-07</v>
+        <v>3.0618e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.2505e-08</v>
+        <v>4.0715e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>4.2581e-08</v>
+        <v>4.0683e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>8.5086e-08</v>
+        <v>8.1399e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>90.69649481773376</v>
+        <v>95.97548413276672</v>
       </c>
     </row>
     <row r="8">
@@ -976,46 +976,46 @@
         <v>0.05</v>
       </c>
       <c r="H8" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I8" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>600000</v>
+        <v>614403</v>
       </c>
       <c r="L8" t="n">
-        <v>800000</v>
+        <v>819204</v>
       </c>
       <c r="M8" t="n">
-        <v>1400000</v>
+        <v>1433607</v>
       </c>
       <c r="N8" t="n">
         <v>1.1497e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>5.7048e-08</v>
+        <v>5.7047e-08</v>
       </c>
       <c r="P8" t="n">
         <v>1.1497e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.2933e-09</v>
+        <v>8.293899999999999e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>4.1559e-09</v>
+        <v>4.1555e-09</v>
       </c>
       <c r="S8" t="n">
         <v>1.2449e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U8" t="n">
-        <v>100.662250995636</v>
+        <v>102.4103710651398</v>
       </c>
     </row>
     <row r="9">
@@ -1045,46 +1045,46 @@
         <v>0.05</v>
       </c>
       <c r="H9" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I9" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>600000</v>
+        <v>614403</v>
       </c>
       <c r="L9" t="n">
-        <v>800000</v>
+        <v>819204</v>
       </c>
       <c r="M9" t="n">
-        <v>1400000</v>
+        <v>1433607</v>
       </c>
       <c r="N9" t="n">
-        <v>2.0862e-07</v>
+        <v>2.0335e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>1.7482e-07</v>
+        <v>1.6825e-07</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0862e-07</v>
+        <v>2.0335e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3672e-08</v>
+        <v>2.2808e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2635e-08</v>
+        <v>2.1687e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>4.6307e-08</v>
+        <v>4.4495e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U9" t="n">
-        <v>114.0216569900513</v>
+        <v>116.907726764679</v>
       </c>
     </row>
     <row r="10">
@@ -1114,46 +1114,46 @@
         <v>0.05</v>
       </c>
       <c r="H10" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I10" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>600000</v>
+        <v>614403</v>
       </c>
       <c r="L10" t="n">
-        <v>800000</v>
+        <v>819204</v>
       </c>
       <c r="M10" t="n">
-        <v>1400000</v>
+        <v>1433607</v>
       </c>
       <c r="N10" t="n">
         <v>1.1492e-07</v>
       </c>
       <c r="O10" t="n">
-        <v>5.7049e-08</v>
+        <v>5.7048e-08</v>
       </c>
       <c r="P10" t="n">
         <v>1.1492e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.315499999999999e-09</v>
+        <v>8.315100000000001e-09</v>
       </c>
       <c r="R10" t="n">
-        <v>4.1307e-09</v>
+        <v>4.1313e-09</v>
       </c>
       <c r="S10" t="n">
         <v>1.2446e-08</v>
       </c>
       <c r="T10" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U10" t="n">
-        <v>70.09029603004456</v>
+        <v>71.28126168251038</v>
       </c>
     </row>
     <row r="11">
@@ -1183,46 +1183,46 @@
         <v>0.05</v>
       </c>
       <c r="H11" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I11" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>800000</v>
+        <v>819204</v>
       </c>
       <c r="L11" t="n">
-        <v>1800000</v>
+        <v>1843209</v>
       </c>
       <c r="M11" t="n">
-        <v>2600000</v>
+        <v>2662413</v>
       </c>
       <c r="N11" t="n">
         <v>1.1493e-07</v>
       </c>
       <c r="O11" t="n">
-        <v>5.7048e-08</v>
+        <v>5.7047e-08</v>
       </c>
       <c r="P11" t="n">
         <v>1.1493e-07</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.320699999999999e-09</v>
+        <v>8.315e-09</v>
       </c>
       <c r="R11" t="n">
-        <v>4.142e-09</v>
+        <v>4.1398e-09</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2463e-08</v>
+        <v>1.2455e-08</v>
       </c>
       <c r="T11" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U11" t="n">
-        <v>84.44520401954651</v>
+        <v>85.24589276313782</v>
       </c>
     </row>
     <row r="12">
@@ -1252,46 +1252,46 @@
         <v>0.02</v>
       </c>
       <c r="H12" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I12" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>400000</v>
+        <v>409602</v>
       </c>
       <c r="L12" t="n">
-        <v>600000</v>
+        <v>614403</v>
       </c>
       <c r="M12" t="n">
-        <v>1000000</v>
+        <v>1024005</v>
       </c>
       <c r="N12" t="n">
-        <v>6.0149e-07</v>
+        <v>5.7581e-07</v>
       </c>
       <c r="O12" t="n">
-        <v>7.652e-07</v>
+        <v>7.3091e-07</v>
       </c>
       <c r="P12" t="n">
-        <v>7.652e-07</v>
+        <v>7.3091e-07</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.1068e-08</v>
+        <v>3.9289e-08</v>
       </c>
       <c r="R12" t="n">
-        <v>4.5279e-08</v>
+        <v>4.3217e-08</v>
       </c>
       <c r="S12" t="n">
-        <v>8.6347e-08</v>
+        <v>8.2506e-08</v>
       </c>
       <c r="T12" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U12" t="n">
-        <v>91.2917652130127</v>
+        <v>95.50071787834167</v>
       </c>
     </row>
     <row r="13">
@@ -1321,46 +1321,46 @@
         <v>0.02</v>
       </c>
       <c r="H13" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I13" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>600000</v>
+        <v>614403</v>
       </c>
       <c r="L13" t="n">
-        <v>800000</v>
+        <v>819204</v>
       </c>
       <c r="M13" t="n">
-        <v>1400000</v>
+        <v>1433607</v>
       </c>
       <c r="N13" t="n">
-        <v>1.247e-07</v>
+        <v>1.2088e-07</v>
       </c>
       <c r="O13" t="n">
-        <v>6.180899999999999e-08</v>
+        <v>5.9914e-08</v>
       </c>
       <c r="P13" t="n">
-        <v>1.247e-07</v>
+        <v>1.2088e-07</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.3449e-09</v>
+        <v>6.2404e-09</v>
       </c>
       <c r="R13" t="n">
-        <v>3.1868e-09</v>
+        <v>3.1342e-09</v>
       </c>
       <c r="S13" t="n">
-        <v>9.5318e-09</v>
+        <v>9.374500000000001e-09</v>
       </c>
       <c r="T13" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U13" t="n">
-        <v>97.52986288070679</v>
+        <v>100.7571110725403</v>
       </c>
     </row>
     <row r="14">
@@ -1390,46 +1390,46 @@
         <v>0.02</v>
       </c>
       <c r="H14" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I14" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>600000</v>
+        <v>614403</v>
       </c>
       <c r="L14" t="n">
-        <v>800000</v>
+        <v>819204</v>
       </c>
       <c r="M14" t="n">
-        <v>1400000</v>
+        <v>1433607</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5272e-07</v>
+        <v>3.3777e-07</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6871e-07</v>
+        <v>3.5235e-07</v>
       </c>
       <c r="P14" t="n">
-        <v>3.6871e-07</v>
+        <v>3.5235e-07</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.3071e-08</v>
+        <v>2.2127e-08</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3043e-08</v>
+        <v>2.2035e-08</v>
       </c>
       <c r="S14" t="n">
-        <v>4.6114e-08</v>
+        <v>4.4162e-08</v>
       </c>
       <c r="T14" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U14" t="n">
-        <v>113.7014091014862</v>
+        <v>119.18785572052</v>
       </c>
     </row>
     <row r="15">
@@ -1459,46 +1459,46 @@
         <v>0.02</v>
       </c>
       <c r="H15" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I15" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>600000</v>
+        <v>614403</v>
       </c>
       <c r="L15" t="n">
-        <v>800000</v>
+        <v>819204</v>
       </c>
       <c r="M15" t="n">
-        <v>1400000</v>
+        <v>1433607</v>
       </c>
       <c r="N15" t="n">
-        <v>9.7226e-08</v>
+        <v>9.7224e-08</v>
       </c>
       <c r="O15" t="n">
         <v>4.8322e-08</v>
       </c>
       <c r="P15" t="n">
-        <v>9.7226e-08</v>
+        <v>9.7224e-08</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.441e-09</v>
+        <v>4.4399e-09</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2019e-09</v>
+        <v>2.1999e-09</v>
       </c>
       <c r="S15" t="n">
-        <v>6.6429e-09</v>
+        <v>6.6397e-09</v>
       </c>
       <c r="T15" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U15" t="n">
-        <v>61.64429903030396</v>
+        <v>65.25774908065796</v>
       </c>
     </row>
     <row r="16">
@@ -1528,22 +1528,22 @@
         <v>0.02</v>
       </c>
       <c r="H16" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I16" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>800000</v>
+        <v>819204</v>
       </c>
       <c r="L16" t="n">
-        <v>1800000</v>
+        <v>1843209</v>
       </c>
       <c r="M16" t="n">
-        <v>2600000</v>
+        <v>2662413</v>
       </c>
       <c r="N16" t="n">
         <v>9.7224e-08</v>
@@ -1555,19 +1555,19 @@
         <v>9.7224e-08</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.9768e-09</v>
+        <v>4.9351e-09</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4861e-09</v>
+        <v>2.4642e-09</v>
       </c>
       <c r="S16" t="n">
-        <v>7.463e-09</v>
+        <v>7.3993e-09</v>
       </c>
       <c r="T16" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U16" t="n">
-        <v>73.00849509239197</v>
+        <v>79.46841979026794</v>
       </c>
     </row>
     <row r="17">
@@ -1597,46 +1597,46 @@
         <v>0.01</v>
       </c>
       <c r="H17" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I17" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>400000</v>
+        <v>409602</v>
       </c>
       <c r="L17" t="n">
-        <v>600000</v>
+        <v>614403</v>
       </c>
       <c r="M17" t="n">
-        <v>1000000</v>
+        <v>1024005</v>
       </c>
       <c r="N17" t="n">
-        <v>9.720800000000001e-07</v>
+        <v>9.2684e-07</v>
       </c>
       <c r="O17" t="n">
-        <v>2.0815e-06</v>
+        <v>1.9855e-06</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0815e-06</v>
+        <v>1.9855e-06</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.7122e-08</v>
+        <v>3.552e-08</v>
       </c>
       <c r="R17" t="n">
-        <v>5.4512e-08</v>
+        <v>5.2034e-08</v>
       </c>
       <c r="S17" t="n">
-        <v>9.1634e-08</v>
+        <v>8.7554e-08</v>
       </c>
       <c r="T17" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U17" t="n">
-        <v>90.55151295661926</v>
+        <v>91.8310239315033</v>
       </c>
     </row>
     <row r="18">
@@ -1666,46 +1666,46 @@
         <v>0.01</v>
       </c>
       <c r="H18" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I18" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>600000</v>
+        <v>614403</v>
       </c>
       <c r="L18" t="n">
-        <v>800000</v>
+        <v>819204</v>
       </c>
       <c r="M18" t="n">
-        <v>1400000</v>
+        <v>1433607</v>
       </c>
       <c r="N18" t="n">
-        <v>6.3453e-07</v>
+        <v>6.0518e-07</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1877e-07</v>
+        <v>3.0407e-07</v>
       </c>
       <c r="P18" t="n">
-        <v>6.3453e-07</v>
+        <v>6.0518e-07</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.6909e-08</v>
+        <v>1.625e-08</v>
       </c>
       <c r="R18" t="n">
-        <v>8.4575e-09</v>
+        <v>8.1284e-09</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5366e-08</v>
+        <v>2.4378e-08</v>
       </c>
       <c r="T18" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U18" t="n">
-        <v>96.37633204460144</v>
+        <v>98.81036901473999</v>
       </c>
     </row>
     <row r="19">
@@ -1735,46 +1735,46 @@
         <v>0.01</v>
       </c>
       <c r="H19" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I19" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>600000</v>
+        <v>614403</v>
       </c>
       <c r="L19" t="n">
-        <v>800000</v>
+        <v>819204</v>
       </c>
       <c r="M19" t="n">
-        <v>1400000</v>
+        <v>1433607</v>
       </c>
       <c r="N19" t="n">
-        <v>5.7877e-07</v>
+        <v>5.5197e-07</v>
       </c>
       <c r="O19" t="n">
-        <v>8.1101e-07</v>
+        <v>7.7364e-07</v>
       </c>
       <c r="P19" t="n">
-        <v>8.1101e-07</v>
+        <v>7.7364e-07</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.2069e-08</v>
+        <v>2.1193e-08</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4261e-08</v>
+        <v>2.3191e-08</v>
       </c>
       <c r="S19" t="n">
-        <v>4.6329e-08</v>
+        <v>4.4385e-08</v>
       </c>
       <c r="T19" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U19" t="n">
-        <v>113.5683410167694</v>
+        <v>127.0266859531403</v>
       </c>
     </row>
     <row r="20">
@@ -1804,46 +1804,46 @@
         <v>0.01</v>
       </c>
       <c r="H20" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I20" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>600000</v>
+        <v>614403</v>
       </c>
       <c r="L20" t="n">
-        <v>800000</v>
+        <v>819204</v>
       </c>
       <c r="M20" t="n">
-        <v>1400000</v>
+        <v>1433607</v>
       </c>
       <c r="N20" t="n">
-        <v>7.4617e-08</v>
+        <v>7.462e-08</v>
       </c>
       <c r="O20" t="n">
-        <v>4.0537e-08</v>
+        <v>3.7985e-08</v>
       </c>
       <c r="P20" t="n">
-        <v>7.4617e-08</v>
+        <v>7.462e-08</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.0018e-09</v>
+        <v>4.0352e-09</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8753e-09</v>
+        <v>1.8612e-09</v>
       </c>
       <c r="S20" t="n">
-        <v>5.8771e-09</v>
+        <v>5.8964e-09</v>
       </c>
       <c r="T20" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U20" t="n">
-        <v>59.06227612495422</v>
+        <v>67.6193950176239</v>
       </c>
     </row>
     <row r="21">
@@ -1873,46 +1873,46 @@
         <v>0.01</v>
       </c>
       <c r="H21" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="I21" t="n">
-        <v>200000</v>
+        <v>204801</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>800000</v>
+        <v>819204</v>
       </c>
       <c r="L21" t="n">
-        <v>1800000</v>
+        <v>1843209</v>
       </c>
       <c r="M21" t="n">
-        <v>2600000</v>
+        <v>2662413</v>
       </c>
       <c r="N21" t="n">
-        <v>2.2558e-07</v>
+        <v>2.1454e-07</v>
       </c>
       <c r="O21" t="n">
-        <v>1.1419e-07</v>
+        <v>1.0865e-07</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2558e-07</v>
+        <v>2.1454e-07</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.8755e-09</v>
+        <v>7.624399999999999e-09</v>
       </c>
       <c r="R21" t="n">
-        <v>3.8719e-09</v>
+        <v>3.7494e-09</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1747e-08</v>
+        <v>1.1374e-08</v>
       </c>
       <c r="T21" t="n">
-        <v>5e-06</v>
+        <v>4.882788658258505e-06</v>
       </c>
       <c r="U21" t="n">
-        <v>69.10936594009399</v>
+        <v>80.31894898414612</v>
       </c>
     </row>
     <row r="22">
@@ -1942,46 +1942,46 @@
         <v>0.1</v>
       </c>
       <c r="H22" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I22" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>200002</v>
+        <v>204802</v>
       </c>
       <c r="L22" t="n">
-        <v>300003</v>
+        <v>307203</v>
       </c>
       <c r="M22" t="n">
-        <v>500005</v>
+        <v>512005</v>
       </c>
       <c r="N22" t="n">
-        <v>7.0148e-07</v>
+        <v>6.7446e-07</v>
       </c>
       <c r="O22" t="n">
-        <v>6.3045e-07</v>
+        <v>6.0307e-07</v>
       </c>
       <c r="P22" t="n">
-        <v>7.0148e-07</v>
+        <v>6.7446e-07</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.4459e-07</v>
+        <v>1.3802e-07</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4553e-07</v>
+        <v>1.3888e-07</v>
       </c>
       <c r="S22" t="n">
-        <v>2.9011e-07</v>
+        <v>2.769e-07</v>
       </c>
       <c r="T22" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U22" t="n">
-        <v>45.15495562553406</v>
+        <v>47.64034008979797</v>
       </c>
     </row>
     <row r="23">
@@ -2011,46 +2011,46 @@
         <v>0.1</v>
       </c>
       <c r="H23" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I23" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>300003</v>
+        <v>307203</v>
       </c>
       <c r="L23" t="n">
-        <v>400004</v>
+        <v>409604</v>
       </c>
       <c r="M23" t="n">
-        <v>700007</v>
+        <v>716807</v>
       </c>
       <c r="N23" t="n">
-        <v>1.1377e-07</v>
+        <v>1.1378e-07</v>
       </c>
       <c r="O23" t="n">
-        <v>5.6723e-08</v>
+        <v>5.6725e-08</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1377e-07</v>
+        <v>1.1378e-07</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.1175e-08</v>
+        <v>1.1174e-08</v>
       </c>
       <c r="R23" t="n">
-        <v>5.5767e-09</v>
+        <v>5.5759e-09</v>
       </c>
       <c r="S23" t="n">
-        <v>1.6752e-08</v>
+        <v>1.675e-08</v>
       </c>
       <c r="T23" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U23" t="n">
-        <v>52.2408127784729</v>
+        <v>53.41447496414185</v>
       </c>
     </row>
     <row r="24">
@@ -2080,46 +2080,46 @@
         <v>0.1</v>
       </c>
       <c r="H24" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I24" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>300003</v>
+        <v>307203</v>
       </c>
       <c r="L24" t="n">
-        <v>400004</v>
+        <v>409604</v>
       </c>
       <c r="M24" t="n">
-        <v>700007</v>
+        <v>716807</v>
       </c>
       <c r="N24" t="n">
-        <v>4.1491e-07</v>
+        <v>4.0093e-07</v>
       </c>
       <c r="O24" t="n">
-        <v>3.3898e-07</v>
+        <v>3.2487e-07</v>
       </c>
       <c r="P24" t="n">
-        <v>4.1491e-07</v>
+        <v>4.0093e-07</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.574400000000001e-08</v>
+        <v>7.241e-08</v>
       </c>
       <c r="R24" t="n">
-        <v>7.472899999999999e-08</v>
+        <v>7.1318e-08</v>
       </c>
       <c r="S24" t="n">
-        <v>1.5047e-07</v>
+        <v>1.4373e-07</v>
       </c>
       <c r="T24" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U24" t="n">
-        <v>58.02921390533447</v>
+        <v>59.43659996986389</v>
       </c>
     </row>
     <row r="25">
@@ -2149,46 +2149,46 @@
         <v>0.1</v>
       </c>
       <c r="H25" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I25" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>300003</v>
+        <v>307203</v>
       </c>
       <c r="L25" t="n">
-        <v>400004</v>
+        <v>409604</v>
       </c>
       <c r="M25" t="n">
-        <v>700007</v>
+        <v>716807</v>
       </c>
       <c r="N25" t="n">
-        <v>1.1438e-07</v>
+        <v>1.1436e-07</v>
       </c>
       <c r="O25" t="n">
-        <v>5.6442e-08</v>
+        <v>5.6431e-08</v>
       </c>
       <c r="P25" t="n">
-        <v>1.1438e-07</v>
+        <v>1.1436e-07</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.1176e-08</v>
+        <v>1.1172e-08</v>
       </c>
       <c r="R25" t="n">
-        <v>5.5459e-09</v>
+        <v>5.5454e-09</v>
       </c>
       <c r="S25" t="n">
-        <v>1.6722e-08</v>
+        <v>1.6718e-08</v>
       </c>
       <c r="T25" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U25" t="n">
-        <v>42.25885891914368</v>
+        <v>43.47129917144775</v>
       </c>
     </row>
     <row r="26">
@@ -2218,46 +2218,46 @@
         <v>0.1</v>
       </c>
       <c r="H26" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I26" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>400004</v>
+        <v>409604</v>
       </c>
       <c r="L26" t="n">
-        <v>900009</v>
+        <v>921609</v>
       </c>
       <c r="M26" t="n">
-        <v>1300013</v>
+        <v>1331213</v>
       </c>
       <c r="N26" t="n">
-        <v>1.1432e-07</v>
+        <v>1.143e-07</v>
       </c>
       <c r="O26" t="n">
-        <v>5.6449e-08</v>
+        <v>5.6465e-08</v>
       </c>
       <c r="P26" t="n">
-        <v>1.1432e-07</v>
+        <v>1.143e-07</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.1187e-08</v>
+        <v>1.119e-08</v>
       </c>
       <c r="R26" t="n">
-        <v>5.5565e-09</v>
+        <v>5.5597e-09</v>
       </c>
       <c r="S26" t="n">
-        <v>1.6743e-08</v>
+        <v>1.675e-08</v>
       </c>
       <c r="T26" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U26" t="n">
-        <v>52.41177797317505</v>
+        <v>52.7157998085022</v>
       </c>
     </row>
     <row r="27">
@@ -2287,46 +2287,46 @@
         <v>0.05</v>
       </c>
       <c r="H27" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I27" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>200002</v>
+        <v>204802</v>
       </c>
       <c r="L27" t="n">
-        <v>300003</v>
+        <v>307203</v>
       </c>
       <c r="M27" t="n">
-        <v>500005</v>
+        <v>512005</v>
       </c>
       <c r="N27" t="n">
-        <v>1.1422e-06</v>
+        <v>1.0917e-06</v>
       </c>
       <c r="O27" t="n">
-        <v>1.1565e-06</v>
+        <v>1.1047e-06</v>
       </c>
       <c r="P27" t="n">
-        <v>1.1565e-06</v>
+        <v>1.1047e-06</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.6189e-07</v>
+        <v>1.545e-07</v>
       </c>
       <c r="R27" t="n">
-        <v>1.6536e-07</v>
+        <v>1.5779e-07</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2726e-07</v>
+        <v>3.1229e-07</v>
       </c>
       <c r="T27" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U27" t="n">
-        <v>45.02338266372681</v>
+        <v>46.42538285255432</v>
       </c>
     </row>
     <row r="28">
@@ -2356,46 +2356,46 @@
         <v>0.05</v>
       </c>
       <c r="H28" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I28" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>300003</v>
+        <v>307203</v>
       </c>
       <c r="L28" t="n">
-        <v>400004</v>
+        <v>409604</v>
       </c>
       <c r="M28" t="n">
-        <v>700007</v>
+        <v>716807</v>
       </c>
       <c r="N28" t="n">
         <v>1.1508e-07</v>
       </c>
       <c r="O28" t="n">
-        <v>5.7095e-08</v>
+        <v>5.7092e-08</v>
       </c>
       <c r="P28" t="n">
         <v>1.1508e-07</v>
       </c>
       <c r="Q28" t="n">
-        <v>8.636800000000001e-09</v>
+        <v>8.5979e-09</v>
       </c>
       <c r="R28" t="n">
-        <v>4.3423e-09</v>
+        <v>4.3236e-09</v>
       </c>
       <c r="S28" t="n">
-        <v>1.2979e-08</v>
+        <v>1.2921e-08</v>
       </c>
       <c r="T28" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U28" t="n">
-        <v>49.78209805488586</v>
+        <v>51.05760097503662</v>
       </c>
     </row>
     <row r="29">
@@ -2425,46 +2425,46 @@
         <v>0.05</v>
       </c>
       <c r="H29" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I29" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>300003</v>
+        <v>307203</v>
       </c>
       <c r="L29" t="n">
-        <v>400004</v>
+        <v>409604</v>
       </c>
       <c r="M29" t="n">
-        <v>700007</v>
+        <v>716807</v>
       </c>
       <c r="N29" t="n">
-        <v>6.1619e-07</v>
+        <v>5.8969e-07</v>
       </c>
       <c r="O29" t="n">
-        <v>6.0202e-07</v>
+        <v>5.7576e-07</v>
       </c>
       <c r="P29" t="n">
-        <v>6.1619e-07</v>
+        <v>5.8969e-07</v>
       </c>
       <c r="Q29" t="n">
-        <v>8.461e-08</v>
+        <v>8.0784e-08</v>
       </c>
       <c r="R29" t="n">
-        <v>8.4656e-08</v>
+        <v>8.0802e-08</v>
       </c>
       <c r="S29" t="n">
-        <v>1.6927e-07</v>
+        <v>1.6159e-07</v>
       </c>
       <c r="T29" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U29" t="n">
-        <v>58.24443483352661</v>
+        <v>59.05711507797241</v>
       </c>
     </row>
     <row r="30">
@@ -2494,46 +2494,46 @@
         <v>0.05</v>
       </c>
       <c r="H30" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I30" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>300003</v>
+        <v>307203</v>
       </c>
       <c r="L30" t="n">
-        <v>400004</v>
+        <v>409604</v>
       </c>
       <c r="M30" t="n">
-        <v>700007</v>
+        <v>716807</v>
       </c>
       <c r="N30" t="n">
         <v>1.1486e-07</v>
       </c>
       <c r="O30" t="n">
-        <v>5.7108e-08</v>
+        <v>5.7104e-08</v>
       </c>
       <c r="P30" t="n">
         <v>1.1486e-07</v>
       </c>
       <c r="Q30" t="n">
-        <v>8.367999999999999e-09</v>
+        <v>8.3638e-09</v>
       </c>
       <c r="R30" t="n">
-        <v>4.1181e-09</v>
+        <v>4.118e-09</v>
       </c>
       <c r="S30" t="n">
-        <v>1.2486e-08</v>
+        <v>1.2482e-08</v>
       </c>
       <c r="T30" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U30" t="n">
-        <v>35.11010408401489</v>
+        <v>36.07424902915955</v>
       </c>
     </row>
     <row r="31">
@@ -2563,46 +2563,46 @@
         <v>0.05</v>
       </c>
       <c r="H31" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I31" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>400004</v>
+        <v>409604</v>
       </c>
       <c r="L31" t="n">
-        <v>900009</v>
+        <v>921609</v>
       </c>
       <c r="M31" t="n">
-        <v>1300013</v>
+        <v>1331213</v>
       </c>
       <c r="N31" t="n">
         <v>1.1493e-07</v>
       </c>
       <c r="O31" t="n">
-        <v>5.7105e-08</v>
+        <v>5.7101e-08</v>
       </c>
       <c r="P31" t="n">
         <v>1.1493e-07</v>
       </c>
       <c r="Q31" t="n">
-        <v>8.3927e-09</v>
+        <v>8.387300000000001e-09</v>
       </c>
       <c r="R31" t="n">
-        <v>4.133e-09</v>
+        <v>4.1345e-09</v>
       </c>
       <c r="S31" t="n">
-        <v>1.2526e-08</v>
+        <v>1.2522e-08</v>
       </c>
       <c r="T31" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U31" t="n">
-        <v>44.13329005241394</v>
+        <v>43.34080505371094</v>
       </c>
     </row>
     <row r="32">
@@ -2632,46 +2632,46 @@
         <v>0.02</v>
       </c>
       <c r="H32" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I32" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>200002</v>
+        <v>204802</v>
       </c>
       <c r="L32" t="n">
-        <v>300003</v>
+        <v>307203</v>
       </c>
       <c r="M32" t="n">
-        <v>500005</v>
+        <v>512005</v>
       </c>
       <c r="N32" t="n">
-        <v>2.2533e-06</v>
+        <v>2.151e-06</v>
       </c>
       <c r="O32" t="n">
-        <v>3.0172e-06</v>
+        <v>2.879e-06</v>
       </c>
       <c r="P32" t="n">
-        <v>3.0172e-06</v>
+        <v>2.879e-06</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.5695e-07</v>
+        <v>1.4979e-07</v>
       </c>
       <c r="R32" t="n">
-        <v>1.7811e-07</v>
+        <v>1.6995e-07</v>
       </c>
       <c r="S32" t="n">
-        <v>3.3506e-07</v>
+        <v>3.1974e-07</v>
       </c>
       <c r="T32" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U32" t="n">
-        <v>44.93844079971313</v>
+        <v>46.30880403518677</v>
       </c>
     </row>
     <row r="33">
@@ -2701,46 +2701,46 @@
         <v>0.02</v>
       </c>
       <c r="H33" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I33" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>300003</v>
+        <v>307203</v>
       </c>
       <c r="L33" t="n">
-        <v>400004</v>
+        <v>409604</v>
       </c>
       <c r="M33" t="n">
-        <v>700007</v>
+        <v>716807</v>
       </c>
       <c r="N33" t="n">
-        <v>3.7732e-07</v>
+        <v>3.5797e-07</v>
       </c>
       <c r="O33" t="n">
-        <v>1.8973e-07</v>
+        <v>1.7767e-07</v>
       </c>
       <c r="P33" t="n">
-        <v>3.7732e-07</v>
+        <v>3.5797e-07</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.4731e-08</v>
+        <v>1.4115e-08</v>
       </c>
       <c r="R33" t="n">
-        <v>7.4109e-09</v>
+        <v>7.0877e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>2.2142e-08</v>
+        <v>2.1203e-08</v>
       </c>
       <c r="T33" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U33" t="n">
-        <v>48.50676608085632</v>
+        <v>49.78737926483154</v>
       </c>
     </row>
     <row r="34">
@@ -2770,46 +2770,46 @@
         <v>0.02</v>
       </c>
       <c r="H34" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I34" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>300003</v>
+        <v>307203</v>
       </c>
       <c r="L34" t="n">
-        <v>400004</v>
+        <v>409604</v>
       </c>
       <c r="M34" t="n">
-        <v>700007</v>
+        <v>716807</v>
       </c>
       <c r="N34" t="n">
-        <v>1.3343e-06</v>
+        <v>1.273e-06</v>
       </c>
       <c r="O34" t="n">
-        <v>1.4362e-06</v>
+        <v>1.3701e-06</v>
       </c>
       <c r="P34" t="n">
-        <v>1.4362e-06</v>
+        <v>1.3701e-06</v>
       </c>
       <c r="Q34" t="n">
-        <v>8.666e-08</v>
+        <v>8.2739e-08</v>
       </c>
       <c r="R34" t="n">
-        <v>8.8587e-08</v>
+        <v>8.4523e-08</v>
       </c>
       <c r="S34" t="n">
-        <v>1.7525e-07</v>
+        <v>1.6726e-07</v>
       </c>
       <c r="T34" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U34" t="n">
-        <v>57.99712300300598</v>
+        <v>59.30117893218994</v>
       </c>
     </row>
     <row r="35">
@@ -2839,46 +2839,46 @@
         <v>0.02</v>
       </c>
       <c r="H35" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I35" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>300003</v>
+        <v>307203</v>
       </c>
       <c r="L35" t="n">
-        <v>400004</v>
+        <v>409604</v>
       </c>
       <c r="M35" t="n">
-        <v>700007</v>
+        <v>716807</v>
       </c>
       <c r="N35" t="n">
-        <v>9.9021e-08</v>
+        <v>9.836e-08</v>
       </c>
       <c r="O35" t="n">
         <v>4.8321e-08</v>
       </c>
       <c r="P35" t="n">
-        <v>9.9021e-08</v>
+        <v>9.836e-08</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.4689e-09</v>
+        <v>4.4621e-09</v>
       </c>
       <c r="R35" t="n">
-        <v>2.3313e-09</v>
+        <v>2.3199e-09</v>
       </c>
       <c r="S35" t="n">
-        <v>6.8002e-09</v>
+        <v>6.782e-09</v>
       </c>
       <c r="T35" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U35" t="n">
-        <v>31.10077309608459</v>
+        <v>32.06406378746033</v>
       </c>
     </row>
     <row r="36">
@@ -2908,46 +2908,46 @@
         <v>0.02</v>
       </c>
       <c r="H36" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I36" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>400004</v>
+        <v>409604</v>
       </c>
       <c r="L36" t="n">
-        <v>900009</v>
+        <v>921609</v>
       </c>
       <c r="M36" t="n">
-        <v>1300013</v>
+        <v>1331213</v>
       </c>
       <c r="N36" t="n">
-        <v>1.705e-07</v>
+        <v>1.6303e-07</v>
       </c>
       <c r="O36" t="n">
-        <v>9.202e-08</v>
+        <v>8.8368e-08</v>
       </c>
       <c r="P36" t="n">
-        <v>1.705e-07</v>
+        <v>1.6303e-07</v>
       </c>
       <c r="Q36" t="n">
-        <v>7.9064e-09</v>
+        <v>7.6834e-09</v>
       </c>
       <c r="R36" t="n">
-        <v>3.9101e-09</v>
+        <v>3.7999e-09</v>
       </c>
       <c r="S36" t="n">
-        <v>1.1816e-08</v>
+        <v>1.1483e-08</v>
       </c>
       <c r="T36" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U36" t="n">
-        <v>38.81727194786072</v>
+        <v>37.92596697807312</v>
       </c>
     </row>
     <row r="37">
@@ -2977,46 +2977,46 @@
         <v>0.01</v>
       </c>
       <c r="H37" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I37" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>200002</v>
+        <v>204802</v>
       </c>
       <c r="L37" t="n">
-        <v>300003</v>
+        <v>307203</v>
       </c>
       <c r="M37" t="n">
-        <v>500005</v>
+        <v>512005</v>
       </c>
       <c r="N37" t="n">
-        <v>3.8862e-06</v>
+        <v>3.7068e-06</v>
       </c>
       <c r="O37" t="n">
-        <v>8.249399999999999e-06</v>
+        <v>7.870600000000001e-06</v>
       </c>
       <c r="P37" t="n">
-        <v>8.249399999999999e-06</v>
+        <v>7.870600000000001e-06</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.4145e-07</v>
+        <v>1.3504e-07</v>
       </c>
       <c r="R37" t="n">
-        <v>2.1434e-07</v>
+        <v>2.0451e-07</v>
       </c>
       <c r="S37" t="n">
-        <v>3.5578e-07</v>
+        <v>3.3955e-07</v>
       </c>
       <c r="T37" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U37" t="n">
-        <v>44.92787718772888</v>
+        <v>46.35614395141602</v>
       </c>
     </row>
     <row r="38">
@@ -3046,46 +3046,46 @@
         <v>0.01</v>
       </c>
       <c r="H38" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I38" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>300003</v>
+        <v>307203</v>
       </c>
       <c r="L38" t="n">
-        <v>400004</v>
+        <v>409604</v>
       </c>
       <c r="M38" t="n">
-        <v>700007</v>
+        <v>716807</v>
       </c>
       <c r="N38" t="n">
-        <v>2.5405e-06</v>
+        <v>2.4234e-06</v>
       </c>
       <c r="O38" t="n">
-        <v>1.2726e-06</v>
+        <v>1.214e-06</v>
       </c>
       <c r="P38" t="n">
-        <v>2.5405e-06</v>
+        <v>2.4234e-06</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.982499999999999e-08</v>
+        <v>5.7176e-08</v>
       </c>
       <c r="R38" t="n">
-        <v>3.0132e-08</v>
+        <v>2.8796e-08</v>
       </c>
       <c r="S38" t="n">
-        <v>8.9957e-08</v>
+        <v>8.5972e-08</v>
       </c>
       <c r="T38" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U38" t="n">
-        <v>48.04630398750305</v>
+        <v>49.26414513587952</v>
       </c>
     </row>
     <row r="39">
@@ -3115,46 +3115,46 @@
         <v>0.01</v>
       </c>
       <c r="H39" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I39" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>300003</v>
+        <v>307203</v>
       </c>
       <c r="L39" t="n">
-        <v>400004</v>
+        <v>409604</v>
       </c>
       <c r="M39" t="n">
-        <v>700007</v>
+        <v>716807</v>
       </c>
       <c r="N39" t="n">
-        <v>2.2916e-06</v>
+        <v>2.1864e-06</v>
       </c>
       <c r="O39" t="n">
-        <v>3.2214e-06</v>
+        <v>3.0732e-06</v>
       </c>
       <c r="P39" t="n">
-        <v>3.2214e-06</v>
+        <v>3.0732e-06</v>
       </c>
       <c r="Q39" t="n">
-        <v>8.189e-08</v>
+        <v>7.8221e-08</v>
       </c>
       <c r="R39" t="n">
-        <v>9.2556e-08</v>
+        <v>8.8324e-08</v>
       </c>
       <c r="S39" t="n">
-        <v>1.7445e-07</v>
+        <v>1.6655e-07</v>
       </c>
       <c r="T39" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U39" t="n">
-        <v>57.81594896316528</v>
+        <v>59.25798988342285</v>
       </c>
     </row>
     <row r="40">
@@ -3184,46 +3184,46 @@
         <v>0.01</v>
       </c>
       <c r="H40" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I40" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>300003</v>
+        <v>307203</v>
       </c>
       <c r="L40" t="n">
-        <v>400004</v>
+        <v>409604</v>
       </c>
       <c r="M40" t="n">
-        <v>700007</v>
+        <v>716807</v>
       </c>
       <c r="N40" t="n">
-        <v>7.462e-08</v>
+        <v>7.4607e-08</v>
       </c>
       <c r="O40" t="n">
-        <v>3.7013e-08</v>
+        <v>3.7006e-08</v>
       </c>
       <c r="P40" t="n">
-        <v>7.462e-08</v>
+        <v>7.4607e-08</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.8291e-09</v>
+        <v>3.8347e-09</v>
       </c>
       <c r="R40" t="n">
-        <v>1.855e-09</v>
+        <v>1.8566e-09</v>
       </c>
       <c r="S40" t="n">
-        <v>5.6841e-09</v>
+        <v>5.6913e-09</v>
       </c>
       <c r="T40" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U40" t="n">
-        <v>29.8612699508667</v>
+        <v>30.78752279281616</v>
       </c>
     </row>
     <row r="41">
@@ -3253,46 +3253,46 @@
         <v>0.01</v>
       </c>
       <c r="H41" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="I41" t="n">
-        <v>100001</v>
+        <v>102401</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>400004</v>
+        <v>409604</v>
       </c>
       <c r="L41" t="n">
-        <v>900009</v>
+        <v>921609</v>
       </c>
       <c r="M41" t="n">
-        <v>1300013</v>
+        <v>1331213</v>
       </c>
       <c r="N41" t="n">
-        <v>2.7603e-06</v>
+        <v>2.6208e-06</v>
       </c>
       <c r="O41" t="n">
-        <v>1.3817e-06</v>
+        <v>1.3118e-06</v>
       </c>
       <c r="P41" t="n">
-        <v>2.7603e-06</v>
+        <v>2.6208e-06</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.3971e-08</v>
+        <v>6.0855e-08</v>
       </c>
       <c r="R41" t="n">
-        <v>3.1582e-08</v>
+        <v>3.0039e-08</v>
       </c>
       <c r="S41" t="n">
-        <v>9.555199999999999e-08</v>
+        <v>9.089499999999999e-08</v>
       </c>
       <c r="T41" t="n">
-        <v>9.999900000999991e-06</v>
+        <v>9.765529633499673e-06</v>
       </c>
       <c r="U41" t="n">
-        <v>37.27263808250427</v>
+        <v>36.55550003051758</v>
       </c>
     </row>
     <row r="42">
@@ -3322,46 +3322,46 @@
         <v>0.1</v>
       </c>
       <c r="H42" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I42" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>100000</v>
+        <v>102402</v>
       </c>
       <c r="L42" t="n">
-        <v>150000</v>
+        <v>153603</v>
       </c>
       <c r="M42" t="n">
-        <v>250000</v>
+        <v>256005</v>
       </c>
       <c r="N42" t="n">
-        <v>2.4157e-06</v>
+        <v>2.311e-06</v>
       </c>
       <c r="O42" t="n">
-        <v>2.3666e-06</v>
+        <v>2.261e-06</v>
       </c>
       <c r="P42" t="n">
-        <v>2.4157e-06</v>
+        <v>2.311e-06</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.6226e-07</v>
+        <v>5.3684e-07</v>
       </c>
       <c r="R42" t="n">
-        <v>5.672499999999999e-07</v>
+        <v>5.416e-07</v>
       </c>
       <c r="S42" t="n">
-        <v>1.1295e-06</v>
+        <v>1.0784e-06</v>
       </c>
       <c r="T42" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U42" t="n">
-        <v>22.63025689125061</v>
+        <v>23.16253304481506</v>
       </c>
     </row>
     <row r="43">
@@ -3391,46 +3391,46 @@
         <v>0.1</v>
       </c>
       <c r="H43" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I43" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>150000</v>
+        <v>153603</v>
       </c>
       <c r="L43" t="n">
-        <v>200000</v>
+        <v>204804</v>
       </c>
       <c r="M43" t="n">
-        <v>350000</v>
+        <v>358407</v>
       </c>
       <c r="N43" t="n">
-        <v>1.1309e-07</v>
+        <v>1.1313e-07</v>
       </c>
       <c r="O43" t="n">
-        <v>5.651e-08</v>
+        <v>5.6525e-08</v>
       </c>
       <c r="P43" t="n">
-        <v>1.1309e-07</v>
+        <v>1.1313e-07</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.139e-08</v>
+        <v>1.1364e-08</v>
       </c>
       <c r="R43" t="n">
-        <v>5.6831e-09</v>
+        <v>5.6697e-09</v>
       </c>
       <c r="S43" t="n">
-        <v>1.7073e-08</v>
+        <v>1.7034e-08</v>
       </c>
       <c r="T43" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U43" t="n">
-        <v>26.49621081352234</v>
+        <v>26.89811992645264</v>
       </c>
     </row>
     <row r="44">
@@ -3460,46 +3460,46 @@
         <v>0.1</v>
       </c>
       <c r="H44" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I44" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>150000</v>
+        <v>153603</v>
       </c>
       <c r="L44" t="n">
-        <v>200000</v>
+        <v>204804</v>
       </c>
       <c r="M44" t="n">
-        <v>350000</v>
+        <v>358407</v>
       </c>
       <c r="N44" t="n">
-        <v>1.3086e-06</v>
+        <v>1.2539e-06</v>
       </c>
       <c r="O44" t="n">
-        <v>1.241e-06</v>
+        <v>1.1858e-06</v>
       </c>
       <c r="P44" t="n">
-        <v>1.3086e-06</v>
+        <v>1.2539e-06</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.93e-07</v>
+        <v>2.7965e-07</v>
       </c>
       <c r="R44" t="n">
-        <v>2.9373e-07</v>
+        <v>2.8034e-07</v>
       </c>
       <c r="S44" t="n">
-        <v>5.8673e-07</v>
+        <v>5.5999e-07</v>
       </c>
       <c r="T44" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U44" t="n">
-        <v>29.18165302276611</v>
+        <v>29.82353806495667</v>
       </c>
     </row>
     <row r="45">
@@ -3529,46 +3529,46 @@
         <v>0.1</v>
       </c>
       <c r="H45" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I45" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>150000</v>
+        <v>153603</v>
       </c>
       <c r="L45" t="n">
-        <v>200000</v>
+        <v>204804</v>
       </c>
       <c r="M45" t="n">
-        <v>350000</v>
+        <v>358407</v>
       </c>
       <c r="N45" t="n">
-        <v>1.16e-07</v>
+        <v>1.1588e-07</v>
       </c>
       <c r="O45" t="n">
-        <v>5.7454e-08</v>
+        <v>5.738e-08</v>
       </c>
       <c r="P45" t="n">
-        <v>1.16e-07</v>
+        <v>1.1588e-07</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.1246e-08</v>
+        <v>1.124e-08</v>
       </c>
       <c r="R45" t="n">
-        <v>5.5539e-09</v>
+        <v>5.5447e-09</v>
       </c>
       <c r="S45" t="n">
-        <v>1.68e-08</v>
+        <v>1.6785e-08</v>
       </c>
       <c r="T45" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U45" t="n">
-        <v>21.40497279167175</v>
+        <v>21.88998985290527</v>
       </c>
     </row>
     <row r="46">
@@ -3598,46 +3598,46 @@
         <v>0.1</v>
       </c>
       <c r="H46" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I46" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>200000</v>
+        <v>204804</v>
       </c>
       <c r="L46" t="n">
-        <v>450000</v>
+        <v>460809</v>
       </c>
       <c r="M46" t="n">
-        <v>650000</v>
+        <v>665613</v>
       </c>
       <c r="N46" t="n">
-        <v>1.1559e-07</v>
+        <v>1.155e-07</v>
       </c>
       <c r="O46" t="n">
-        <v>5.6025e-08</v>
+        <v>5.6033e-08</v>
       </c>
       <c r="P46" t="n">
-        <v>1.1559e-07</v>
+        <v>1.155e-07</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.131e-08</v>
+        <v>1.13e-08</v>
       </c>
       <c r="R46" t="n">
-        <v>5.5766e-09</v>
+        <v>5.57e-09</v>
       </c>
       <c r="S46" t="n">
-        <v>1.6886e-08</v>
+        <v>1.687e-08</v>
       </c>
       <c r="T46" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U46" t="n">
-        <v>26.16603302955627</v>
+        <v>27.37155318260193</v>
       </c>
     </row>
     <row r="47">
@@ -3667,46 +3667,46 @@
         <v>0.05</v>
       </c>
       <c r="H47" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I47" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>100000</v>
+        <v>102402</v>
       </c>
       <c r="L47" t="n">
-        <v>150000</v>
+        <v>153603</v>
       </c>
       <c r="M47" t="n">
-        <v>250000</v>
+        <v>256005</v>
       </c>
       <c r="N47" t="n">
-        <v>4.3392e-06</v>
+        <v>4.1448e-06</v>
       </c>
       <c r="O47" t="n">
-        <v>4.4865e-06</v>
+        <v>4.2837e-06</v>
       </c>
       <c r="P47" t="n">
-        <v>4.4865e-06</v>
+        <v>4.2837e-06</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.3068e-07</v>
+        <v>6.0218e-07</v>
       </c>
       <c r="R47" t="n">
-        <v>6.4558e-07</v>
+        <v>6.1637e-07</v>
       </c>
       <c r="S47" t="n">
-        <v>1.2763e-06</v>
+        <v>1.2185e-06</v>
       </c>
       <c r="T47" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U47" t="n">
-        <v>22.61562085151672</v>
+        <v>23.02539205551147</v>
       </c>
     </row>
     <row r="48">
@@ -3736,46 +3736,46 @@
         <v>0.05</v>
       </c>
       <c r="H48" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I48" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>150000</v>
+        <v>153603</v>
       </c>
       <c r="L48" t="n">
-        <v>200000</v>
+        <v>204804</v>
       </c>
       <c r="M48" t="n">
-        <v>350000</v>
+        <v>358407</v>
       </c>
       <c r="N48" t="n">
-        <v>1.3949e-07</v>
+        <v>1.3564e-07</v>
       </c>
       <c r="O48" t="n">
-        <v>7.246499999999999e-08</v>
+        <v>6.9902e-08</v>
       </c>
       <c r="P48" t="n">
-        <v>1.3949e-07</v>
+        <v>1.3564e-07</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.1844e-08</v>
+        <v>1.1572e-08</v>
       </c>
       <c r="R48" t="n">
-        <v>6.1881e-09</v>
+        <v>6.0433e-09</v>
       </c>
       <c r="S48" t="n">
-        <v>1.8032e-08</v>
+        <v>1.7615e-08</v>
       </c>
       <c r="T48" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U48" t="n">
-        <v>25.33507204055786</v>
+        <v>25.63572311401367</v>
       </c>
     </row>
     <row r="49">
@@ -3805,46 +3805,46 @@
         <v>0.05</v>
       </c>
       <c r="H49" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I49" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>150000</v>
+        <v>153603</v>
       </c>
       <c r="L49" t="n">
-        <v>200000</v>
+        <v>204804</v>
       </c>
       <c r="M49" t="n">
-        <v>350000</v>
+        <v>358407</v>
       </c>
       <c r="N49" t="n">
-        <v>2.3109e-06</v>
+        <v>2.2072e-06</v>
       </c>
       <c r="O49" t="n">
-        <v>2.3051e-06</v>
+        <v>2.2001e-06</v>
       </c>
       <c r="P49" t="n">
-        <v>2.3109e-06</v>
+        <v>2.2072e-06</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.3125e-07</v>
+        <v>3.1614e-07</v>
       </c>
       <c r="R49" t="n">
-        <v>3.3274e-07</v>
+        <v>3.1755e-07</v>
       </c>
       <c r="S49" t="n">
-        <v>6.6399e-07</v>
+        <v>6.3369e-07</v>
       </c>
       <c r="T49" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U49" t="n">
-        <v>29.08950614929199</v>
+        <v>29.76742506027222</v>
       </c>
     </row>
     <row r="50">
@@ -3874,46 +3874,46 @@
         <v>0.05</v>
       </c>
       <c r="H50" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I50" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>150000</v>
+        <v>153603</v>
       </c>
       <c r="L50" t="n">
-        <v>200000</v>
+        <v>204804</v>
       </c>
       <c r="M50" t="n">
-        <v>350000</v>
+        <v>358407</v>
       </c>
       <c r="N50" t="n">
-        <v>1.1478e-07</v>
+        <v>1.1479e-07</v>
       </c>
       <c r="O50" t="n">
-        <v>5.7181e-08</v>
+        <v>5.7174e-08</v>
       </c>
       <c r="P50" t="n">
-        <v>1.1478e-07</v>
+        <v>1.1479e-07</v>
       </c>
       <c r="Q50" t="n">
-        <v>8.4155e-09</v>
+        <v>8.404e-09</v>
       </c>
       <c r="R50" t="n">
-        <v>4.1835e-09</v>
+        <v>4.1721e-09</v>
       </c>
       <c r="S50" t="n">
-        <v>1.2599e-08</v>
+        <v>1.2576e-08</v>
       </c>
       <c r="T50" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U50" t="n">
-        <v>17.78175377845764</v>
+        <v>18.22352623939514</v>
       </c>
     </row>
     <row r="51">
@@ -3943,46 +3943,46 @@
         <v>0.05</v>
       </c>
       <c r="H51" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I51" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>200000</v>
+        <v>204804</v>
       </c>
       <c r="L51" t="n">
-        <v>450000</v>
+        <v>460809</v>
       </c>
       <c r="M51" t="n">
-        <v>650000</v>
+        <v>665613</v>
       </c>
       <c r="N51" t="n">
         <v>1.1488e-07</v>
       </c>
       <c r="O51" t="n">
-        <v>6.5809e-08</v>
+        <v>6.4088e-08</v>
       </c>
       <c r="P51" t="n">
         <v>1.1488e-07</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.0019e-08</v>
+        <v>9.873500000000001e-09</v>
       </c>
       <c r="R51" t="n">
-        <v>4.657e-09</v>
+        <v>4.5988e-09</v>
       </c>
       <c r="S51" t="n">
-        <v>1.4676e-08</v>
+        <v>1.4472e-08</v>
       </c>
       <c r="T51" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U51" t="n">
-        <v>21.42535495758057</v>
+        <v>22.56556582450867</v>
       </c>
     </row>
     <row r="52">
@@ -4012,46 +4012,46 @@
         <v>0.02</v>
       </c>
       <c r="H52" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I52" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>100000</v>
+        <v>102402</v>
       </c>
       <c r="L52" t="n">
-        <v>150000</v>
+        <v>153603</v>
       </c>
       <c r="M52" t="n">
-        <v>250000</v>
+        <v>256005</v>
       </c>
       <c r="N52" t="n">
-        <v>8.7258e-06</v>
+        <v>8.3331e-06</v>
       </c>
       <c r="O52" t="n">
-        <v>1.1797e-05</v>
+        <v>1.1263e-05</v>
       </c>
       <c r="P52" t="n">
-        <v>1.1797e-05</v>
+        <v>1.1263e-05</v>
       </c>
       <c r="Q52" t="n">
-        <v>6.1037e-07</v>
+        <v>5.8283e-07</v>
       </c>
       <c r="R52" t="n">
-        <v>6.9584e-07</v>
+        <v>6.6434e-07</v>
       </c>
       <c r="S52" t="n">
-        <v>1.3062e-06</v>
+        <v>1.2472e-06</v>
       </c>
       <c r="T52" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U52" t="n">
-        <v>22.56517314910889</v>
+        <v>23.10089993476868</v>
       </c>
     </row>
     <row r="53">
@@ -4081,46 +4081,46 @@
         <v>0.02</v>
       </c>
       <c r="H53" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I53" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>150000</v>
+        <v>153603</v>
       </c>
       <c r="L53" t="n">
-        <v>200000</v>
+        <v>204804</v>
       </c>
       <c r="M53" t="n">
-        <v>350000</v>
+        <v>358407</v>
       </c>
       <c r="N53" t="n">
-        <v>1.3866e-06</v>
+        <v>1.3238e-06</v>
       </c>
       <c r="O53" t="n">
-        <v>7.2376e-07</v>
+        <v>6.9115e-07</v>
       </c>
       <c r="P53" t="n">
-        <v>1.3866e-06</v>
+        <v>1.3238e-06</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.2427e-08</v>
+        <v>5.0112e-08</v>
       </c>
       <c r="R53" t="n">
-        <v>2.5992e-08</v>
+        <v>2.4846e-08</v>
       </c>
       <c r="S53" t="n">
-        <v>7.8419e-08</v>
+        <v>7.4958e-08</v>
       </c>
       <c r="T53" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U53" t="n">
-        <v>24.59482073783875</v>
+        <v>24.94702482223511</v>
       </c>
     </row>
     <row r="54">
@@ -4150,46 +4150,46 @@
         <v>0.02</v>
       </c>
       <c r="H54" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I54" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>150000</v>
+        <v>153603</v>
       </c>
       <c r="L54" t="n">
-        <v>200000</v>
+        <v>204804</v>
       </c>
       <c r="M54" t="n">
-        <v>350000</v>
+        <v>358407</v>
       </c>
       <c r="N54" t="n">
-        <v>5.2505e-06</v>
+        <v>5.011e-06</v>
       </c>
       <c r="O54" t="n">
-        <v>5.6619e-06</v>
+        <v>5.4034e-06</v>
       </c>
       <c r="P54" t="n">
-        <v>5.6619e-06</v>
+        <v>5.4034e-06</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.3932e-07</v>
+        <v>3.2385e-07</v>
       </c>
       <c r="R54" t="n">
-        <v>3.4915e-07</v>
+        <v>3.3321e-07</v>
       </c>
       <c r="S54" t="n">
-        <v>6.8847e-07</v>
+        <v>6.5706e-07</v>
       </c>
       <c r="T54" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U54" t="n">
-        <v>29.12517404556274</v>
+        <v>29.73892498016357</v>
       </c>
     </row>
     <row r="55">
@@ -4219,46 +4219,46 @@
         <v>0.02</v>
       </c>
       <c r="H55" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I55" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>150000</v>
+        <v>153603</v>
       </c>
       <c r="L55" t="n">
-        <v>200000</v>
+        <v>204804</v>
       </c>
       <c r="M55" t="n">
-        <v>350000</v>
+        <v>358407</v>
       </c>
       <c r="N55" t="n">
-        <v>9.7497e-08</v>
+        <v>9.7216e-08</v>
       </c>
       <c r="O55" t="n">
-        <v>4.8321e-08</v>
+        <v>4.8317e-08</v>
       </c>
       <c r="P55" t="n">
-        <v>9.7497e-08</v>
+        <v>9.7216e-08</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.5377e-09</v>
+        <v>4.5339e-09</v>
       </c>
       <c r="R55" t="n">
-        <v>2.2475e-09</v>
+        <v>2.2417e-09</v>
       </c>
       <c r="S55" t="n">
-        <v>6.7852e-09</v>
+        <v>6.7756e-09</v>
       </c>
       <c r="T55" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U55" t="n">
-        <v>15.74571990966797</v>
+        <v>16.16590690612793</v>
       </c>
     </row>
     <row r="56">
@@ -4288,46 +4288,46 @@
         <v>0.02</v>
       </c>
       <c r="H56" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I56" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>200000</v>
+        <v>204804</v>
       </c>
       <c r="L56" t="n">
-        <v>450000</v>
+        <v>460809</v>
       </c>
       <c r="M56" t="n">
-        <v>650000</v>
+        <v>665613</v>
       </c>
       <c r="N56" t="n">
-        <v>1.4204e-06</v>
+        <v>1.3578e-06</v>
       </c>
       <c r="O56" t="n">
-        <v>7.0013e-07</v>
+        <v>6.7296e-07</v>
       </c>
       <c r="P56" t="n">
-        <v>1.4204e-06</v>
+        <v>1.3578e-06</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.1163e-08</v>
+        <v>4.8844e-08</v>
       </c>
       <c r="R56" t="n">
-        <v>2.5751e-08</v>
+        <v>2.4575e-08</v>
       </c>
       <c r="S56" t="n">
-        <v>7.6914e-08</v>
+        <v>7.3419e-08</v>
       </c>
       <c r="T56" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U56" t="n">
-        <v>18.73041772842407</v>
+        <v>19.94491219520569</v>
       </c>
     </row>
     <row r="57">
@@ -4357,46 +4357,46 @@
         <v>0.01</v>
       </c>
       <c r="H57" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I57" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>100000</v>
+        <v>102402</v>
       </c>
       <c r="L57" t="n">
-        <v>150000</v>
+        <v>153603</v>
       </c>
       <c r="M57" t="n">
-        <v>250000</v>
+        <v>256005</v>
       </c>
       <c r="N57" t="n">
-        <v>1.5391e-05</v>
+        <v>1.4685e-05</v>
       </c>
       <c r="O57" t="n">
-        <v>3.2396e-05</v>
+        <v>3.0921e-05</v>
       </c>
       <c r="P57" t="n">
-        <v>3.2396e-05</v>
+        <v>3.0921e-05</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.4803e-07</v>
+        <v>5.2331e-07</v>
       </c>
       <c r="R57" t="n">
-        <v>8.4e-07</v>
+        <v>8.0184e-07</v>
       </c>
       <c r="S57" t="n">
-        <v>1.388e-06</v>
+        <v>1.3252e-06</v>
       </c>
       <c r="T57" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U57" t="n">
-        <v>22.56520581245422</v>
+        <v>23.07511496543884</v>
       </c>
     </row>
     <row r="58">
@@ -4426,46 +4426,46 @@
         <v>0.01</v>
       </c>
       <c r="H58" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I58" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>150000</v>
+        <v>153603</v>
       </c>
       <c r="L58" t="n">
-        <v>200000</v>
+        <v>204804</v>
       </c>
       <c r="M58" t="n">
-        <v>350000</v>
+        <v>358407</v>
       </c>
       <c r="N58" t="n">
-        <v>1.0042e-05</v>
+        <v>9.581399999999999e-06</v>
       </c>
       <c r="O58" t="n">
-        <v>5.0266e-06</v>
+        <v>4.7964e-06</v>
       </c>
       <c r="P58" t="n">
-        <v>1.0042e-05</v>
+        <v>9.581399999999999e-06</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.3044e-07</v>
+        <v>2.1997e-07</v>
       </c>
       <c r="R58" t="n">
-        <v>1.1609e-07</v>
+        <v>1.1081e-07</v>
       </c>
       <c r="S58" t="n">
-        <v>3.4654e-07</v>
+        <v>3.3078e-07</v>
       </c>
       <c r="T58" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U58" t="n">
-        <v>24.31726217269897</v>
+        <v>24.66714978218079</v>
       </c>
     </row>
     <row r="59">
@@ -4495,46 +4495,46 @@
         <v>0.01</v>
       </c>
       <c r="H59" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I59" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>150000</v>
+        <v>153603</v>
       </c>
       <c r="L59" t="n">
-        <v>200000</v>
+        <v>204804</v>
       </c>
       <c r="M59" t="n">
-        <v>350000</v>
+        <v>358407</v>
       </c>
       <c r="N59" t="n">
-        <v>9.004999999999999e-06</v>
+        <v>8.5949e-06</v>
       </c>
       <c r="O59" t="n">
-        <v>1.2705e-05</v>
+        <v>1.2124e-05</v>
       </c>
       <c r="P59" t="n">
-        <v>1.2705e-05</v>
+        <v>1.2124e-05</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.1896e-07</v>
+        <v>3.0443e-07</v>
       </c>
       <c r="R59" t="n">
-        <v>3.6456e-07</v>
+        <v>3.4791e-07</v>
       </c>
       <c r="S59" t="n">
-        <v>6.8352e-07</v>
+        <v>6.5234e-07</v>
       </c>
       <c r="T59" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U59" t="n">
-        <v>29.06727409362793</v>
+        <v>29.84428811073303</v>
       </c>
     </row>
     <row r="60">
@@ -4564,46 +4564,46 @@
         <v>0.01</v>
       </c>
       <c r="H60" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I60" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>150000</v>
+        <v>153603</v>
       </c>
       <c r="L60" t="n">
-        <v>200000</v>
+        <v>204804</v>
       </c>
       <c r="M60" t="n">
-        <v>350000</v>
+        <v>358407</v>
       </c>
       <c r="N60" t="n">
-        <v>7.462300000000001e-08</v>
+        <v>7.4632e-08</v>
       </c>
       <c r="O60" t="n">
-        <v>6.029199999999999e-08</v>
+        <v>5.6999e-08</v>
       </c>
       <c r="P60" t="n">
-        <v>7.462300000000001e-08</v>
+        <v>7.4632e-08</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.9737e-09</v>
+        <v>3.9445e-09</v>
       </c>
       <c r="R60" t="n">
-        <v>2.1898e-09</v>
+        <v>2.1388e-09</v>
       </c>
       <c r="S60" t="n">
-        <v>6.1635e-09</v>
+        <v>6.0833e-09</v>
       </c>
       <c r="T60" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U60" t="n">
-        <v>15.01282095909119</v>
+        <v>15.37516307830811</v>
       </c>
     </row>
     <row r="61">
@@ -4633,46 +4633,46 @@
         <v>0.01</v>
       </c>
       <c r="H61" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="I61" t="n">
-        <v>50000</v>
+        <v>51201</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>200000</v>
+        <v>204804</v>
       </c>
       <c r="L61" t="n">
-        <v>450000</v>
+        <v>460809</v>
       </c>
       <c r="M61" t="n">
-        <v>650000</v>
+        <v>665613</v>
       </c>
       <c r="N61" t="n">
-        <v>4.2233e-07</v>
+        <v>3.984e-07</v>
       </c>
       <c r="O61" t="n">
-        <v>1.7923e-07</v>
+        <v>1.693e-07</v>
       </c>
       <c r="P61" t="n">
-        <v>4.2233e-07</v>
+        <v>3.984e-07</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.1689e-08</v>
+        <v>1.1446e-08</v>
       </c>
       <c r="R61" t="n">
-        <v>5.8379e-09</v>
+        <v>5.7043e-09</v>
       </c>
       <c r="S61" t="n">
-        <v>1.7527e-08</v>
+        <v>1.715e-08</v>
       </c>
       <c r="T61" t="n">
-        <v>2e-05</v>
+        <v>1.953086853772387e-05</v>
       </c>
       <c r="U61" t="n">
-        <v>17.84374690055847</v>
+        <v>18.95923900604248</v>
       </c>
     </row>
     <row r="62">
@@ -4702,46 +4702,46 @@
         <v>0.1</v>
       </c>
       <c r="H62" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I62" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>51284</v>
+        <v>51202</v>
       </c>
       <c r="L62" t="n">
-        <v>76926</v>
+        <v>76803</v>
       </c>
       <c r="M62" t="n">
-        <v>128210</v>
+        <v>128005</v>
       </c>
       <c r="N62" t="n">
-        <v>8.260900000000001e-06</v>
+        <v>8.5357e-06</v>
       </c>
       <c r="O62" t="n">
-        <v>8.265e-06</v>
+        <v>8.5408e-06</v>
       </c>
       <c r="P62" t="n">
-        <v>8.265e-06</v>
+        <v>8.5408e-06</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.9816e-06</v>
+        <v>2.0485e-06</v>
       </c>
       <c r="R62" t="n">
-        <v>2.0001e-06</v>
+        <v>2.067e-06</v>
       </c>
       <c r="S62" t="n">
-        <v>3.9817e-06</v>
+        <v>4.1155e-06</v>
       </c>
       <c r="T62" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U62" t="n">
-        <v>11.64250516891479</v>
+        <v>11.604984998703</v>
       </c>
     </row>
     <row r="63">
@@ -4771,46 +4771,46 @@
         <v>0.1</v>
       </c>
       <c r="H63" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I63" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>76926</v>
+        <v>76803</v>
       </c>
       <c r="L63" t="n">
-        <v>102568</v>
+        <v>102404</v>
       </c>
       <c r="M63" t="n">
-        <v>179494</v>
+        <v>179207</v>
       </c>
       <c r="N63" t="n">
-        <v>1.2821e-07</v>
+        <v>1.2868e-07</v>
       </c>
       <c r="O63" t="n">
-        <v>5.9523e-08</v>
+        <v>5.9598e-08</v>
       </c>
       <c r="P63" t="n">
-        <v>1.2821e-07</v>
+        <v>1.2868e-07</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.4973e-08</v>
+        <v>1.5011e-08</v>
       </c>
       <c r="R63" t="n">
-        <v>7.2615e-09</v>
+        <v>7.2715e-09</v>
       </c>
       <c r="S63" t="n">
-        <v>2.2235e-08</v>
+        <v>2.2282e-08</v>
       </c>
       <c r="T63" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U63" t="n">
-        <v>13.53322887420654</v>
+        <v>13.53640913963318</v>
       </c>
     </row>
     <row r="64">
@@ -4840,46 +4840,46 @@
         <v>0.1</v>
       </c>
       <c r="H64" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I64" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>76926</v>
+        <v>76803</v>
       </c>
       <c r="L64" t="n">
-        <v>102568</v>
+        <v>102404</v>
       </c>
       <c r="M64" t="n">
-        <v>179494</v>
+        <v>179207</v>
       </c>
       <c r="N64" t="n">
-        <v>4.4087e-06</v>
+        <v>4.5536e-06</v>
       </c>
       <c r="O64" t="n">
-        <v>4.3585e-06</v>
+        <v>4.5038e-06</v>
       </c>
       <c r="P64" t="n">
-        <v>4.4087e-06</v>
+        <v>4.5536e-06</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.048e-06</v>
+        <v>1.0833e-06</v>
       </c>
       <c r="R64" t="n">
-        <v>1.0508e-06</v>
+        <v>1.0861e-06</v>
       </c>
       <c r="S64" t="n">
-        <v>2.0988e-06</v>
+        <v>2.1694e-06</v>
       </c>
       <c r="T64" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U64" t="n">
-        <v>14.90206408500671</v>
+        <v>14.89382100105286</v>
       </c>
     </row>
     <row r="65">
@@ -4909,46 +4909,46 @@
         <v>0.1</v>
       </c>
       <c r="H65" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I65" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>76926</v>
+        <v>76803</v>
       </c>
       <c r="L65" t="n">
-        <v>102568</v>
+        <v>102404</v>
       </c>
       <c r="M65" t="n">
-        <v>179494</v>
+        <v>179207</v>
       </c>
       <c r="N65" t="n">
-        <v>1.1258e-07</v>
+        <v>1.1254e-07</v>
       </c>
       <c r="O65" t="n">
-        <v>5.786e-08</v>
+        <v>5.7902e-08</v>
       </c>
       <c r="P65" t="n">
-        <v>1.1258e-07</v>
+        <v>1.1254e-07</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.1066e-08</v>
+        <v>1.1064e-08</v>
       </c>
       <c r="R65" t="n">
-        <v>5.5999e-09</v>
+        <v>5.6026e-09</v>
       </c>
       <c r="S65" t="n">
-        <v>1.6666e-08</v>
+        <v>1.6667e-08</v>
       </c>
       <c r="T65" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U65" t="n">
-        <v>11.24012494087219</v>
+        <v>11.27159595489502</v>
       </c>
     </row>
     <row r="66">
@@ -4978,46 +4978,46 @@
         <v>0.1</v>
       </c>
       <c r="H66" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I66" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>102568</v>
+        <v>102404</v>
       </c>
       <c r="L66" t="n">
-        <v>230778</v>
+        <v>230409</v>
       </c>
       <c r="M66" t="n">
-        <v>333346</v>
+        <v>332813</v>
       </c>
       <c r="N66" t="n">
-        <v>1.3201e-07</v>
+        <v>1.3263e-07</v>
       </c>
       <c r="O66" t="n">
-        <v>1.025e-07</v>
+        <v>1.0418e-07</v>
       </c>
       <c r="P66" t="n">
-        <v>1.3201e-07</v>
+        <v>1.3263e-07</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.4452e-08</v>
+        <v>1.4606e-08</v>
       </c>
       <c r="R66" t="n">
-        <v>9.7155e-09</v>
+        <v>9.924e-09</v>
       </c>
       <c r="S66" t="n">
-        <v>2.4167e-08</v>
+        <v>2.453e-08</v>
       </c>
       <c r="T66" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U66" t="n">
-        <v>13.4969847202301</v>
+        <v>13.9208550453186</v>
       </c>
     </row>
     <row r="67">
@@ -5047,46 +5047,46 @@
         <v>0.05</v>
       </c>
       <c r="H67" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I67" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>51284</v>
+        <v>51202</v>
       </c>
       <c r="L67" t="n">
-        <v>76926</v>
+        <v>76803</v>
       </c>
       <c r="M67" t="n">
-        <v>128210</v>
+        <v>128005</v>
       </c>
       <c r="N67" t="n">
-        <v>1.5176e-05</v>
+        <v>1.5696e-05</v>
       </c>
       <c r="O67" t="n">
-        <v>1.5824e-05</v>
+        <v>1.6348e-05</v>
       </c>
       <c r="P67" t="n">
-        <v>1.5824e-05</v>
+        <v>1.6348e-05</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.2207e-06</v>
+        <v>2.2965e-06</v>
       </c>
       <c r="R67" t="n">
-        <v>2.2779e-06</v>
+        <v>2.3538e-06</v>
       </c>
       <c r="S67" t="n">
-        <v>4.4987e-06</v>
+        <v>4.6503e-06</v>
       </c>
       <c r="T67" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U67" t="n">
-        <v>11.6442699432373</v>
+        <v>11.58369398117065</v>
       </c>
     </row>
     <row r="68">
@@ -5116,46 +5116,46 @@
         <v>0.05</v>
       </c>
       <c r="H68" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I68" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>76926</v>
+        <v>76803</v>
       </c>
       <c r="L68" t="n">
-        <v>102568</v>
+        <v>102404</v>
       </c>
       <c r="M68" t="n">
-        <v>179494</v>
+        <v>179207</v>
       </c>
       <c r="N68" t="n">
-        <v>4.017e-07</v>
+        <v>4.0256e-07</v>
       </c>
       <c r="O68" t="n">
-        <v>2.1822e-07</v>
+        <v>2.191e-07</v>
       </c>
       <c r="P68" t="n">
-        <v>4.017e-07</v>
+        <v>4.0256e-07</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3685e-08</v>
+        <v>3.381e-08</v>
       </c>
       <c r="R68" t="n">
-        <v>1.6368e-08</v>
+        <v>1.6427e-08</v>
       </c>
       <c r="S68" t="n">
-        <v>5.0053e-08</v>
+        <v>5.0237e-08</v>
       </c>
       <c r="T68" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U68" t="n">
-        <v>12.84522294998169</v>
+        <v>12.84001493453979</v>
       </c>
     </row>
     <row r="69">
@@ -5185,46 +5185,46 @@
         <v>0.05</v>
       </c>
       <c r="H69" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I69" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>76926</v>
+        <v>76803</v>
       </c>
       <c r="L69" t="n">
-        <v>102568</v>
+        <v>102404</v>
       </c>
       <c r="M69" t="n">
-        <v>179494</v>
+        <v>179207</v>
       </c>
       <c r="N69" t="n">
-        <v>8.165999999999999e-06</v>
+        <v>8.4405e-06</v>
       </c>
       <c r="O69" t="n">
-        <v>8.240099999999999e-06</v>
+        <v>8.5161e-06</v>
       </c>
       <c r="P69" t="n">
-        <v>8.240099999999999e-06</v>
+        <v>8.5161e-06</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.1846e-06</v>
+        <v>1.2246e-06</v>
       </c>
       <c r="R69" t="n">
-        <v>1.1912e-06</v>
+        <v>1.2312e-06</v>
       </c>
       <c r="S69" t="n">
-        <v>2.3759e-06</v>
+        <v>2.4558e-06</v>
       </c>
       <c r="T69" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U69" t="n">
-        <v>14.85673904418945</v>
+        <v>14.87357306480408</v>
       </c>
     </row>
     <row r="70">
@@ -5254,46 +5254,46 @@
         <v>0.05</v>
       </c>
       <c r="H70" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I70" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>76926</v>
+        <v>76803</v>
       </c>
       <c r="L70" t="n">
-        <v>102568</v>
+        <v>102404</v>
       </c>
       <c r="M70" t="n">
-        <v>179494</v>
+        <v>179207</v>
       </c>
       <c r="N70" t="n">
-        <v>1.1474e-07</v>
+        <v>1.1473e-07</v>
       </c>
       <c r="O70" t="n">
-        <v>5.7232e-08</v>
+        <v>5.7239e-08</v>
       </c>
       <c r="P70" t="n">
-        <v>1.1474e-07</v>
+        <v>1.1473e-07</v>
       </c>
       <c r="Q70" t="n">
-        <v>8.6174e-09</v>
+        <v>8.6359e-09</v>
       </c>
       <c r="R70" t="n">
-        <v>4.1103e-09</v>
+        <v>4.1171e-09</v>
       </c>
       <c r="S70" t="n">
-        <v>1.2728e-08</v>
+        <v>1.2753e-08</v>
       </c>
       <c r="T70" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U70" t="n">
-        <v>9.338711023330688</v>
+        <v>9.389973163604736</v>
       </c>
     </row>
     <row r="71">
@@ -5323,46 +5323,46 @@
         <v>0.05</v>
       </c>
       <c r="H71" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I71" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>102568</v>
+        <v>102404</v>
       </c>
       <c r="L71" t="n">
-        <v>230778</v>
+        <v>230409</v>
       </c>
       <c r="M71" t="n">
-        <v>333346</v>
+        <v>332813</v>
       </c>
       <c r="N71" t="n">
-        <v>2.8633e-07</v>
+        <v>2.878e-07</v>
       </c>
       <c r="O71" t="n">
-        <v>1.9359e-07</v>
+        <v>1.951e-07</v>
       </c>
       <c r="P71" t="n">
-        <v>2.8633e-07</v>
+        <v>2.878e-07</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.4212e-08</v>
+        <v>2.4274e-08</v>
       </c>
       <c r="R71" t="n">
-        <v>1.3413e-08</v>
+        <v>1.3503e-08</v>
       </c>
       <c r="S71" t="n">
-        <v>3.7625e-08</v>
+        <v>3.7776e-08</v>
       </c>
       <c r="T71" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U71" t="n">
-        <v>11.03507208824158</v>
+        <v>11.6566641330719</v>
       </c>
     </row>
     <row r="72">
@@ -5392,46 +5392,46 @@
         <v>0.02</v>
       </c>
       <c r="H72" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I72" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>51284</v>
+        <v>51202</v>
       </c>
       <c r="L72" t="n">
-        <v>76926</v>
+        <v>76803</v>
       </c>
       <c r="M72" t="n">
-        <v>128210</v>
+        <v>128005</v>
       </c>
       <c r="N72" t="n">
-        <v>3.0334e-05</v>
+        <v>3.1545e-05</v>
       </c>
       <c r="O72" t="n">
-        <v>4.1883e-05</v>
+        <v>4.3158e-05</v>
       </c>
       <c r="P72" t="n">
-        <v>4.1883e-05</v>
+        <v>4.3158e-05</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.1377e-06</v>
+        <v>2.216e-06</v>
       </c>
       <c r="R72" t="n">
-        <v>2.4613e-06</v>
+        <v>2.5405e-06</v>
       </c>
       <c r="S72" t="n">
-        <v>4.599e-06</v>
+        <v>4.7564e-06</v>
       </c>
       <c r="T72" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U72" t="n">
-        <v>11.62911605834961</v>
+        <v>11.61840581893921</v>
       </c>
     </row>
     <row r="73">
@@ -5461,46 +5461,46 @@
         <v>0.02</v>
       </c>
       <c r="H73" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I73" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>76926</v>
+        <v>76803</v>
       </c>
       <c r="L73" t="n">
-        <v>102568</v>
+        <v>102404</v>
       </c>
       <c r="M73" t="n">
-        <v>179494</v>
+        <v>179207</v>
       </c>
       <c r="N73" t="n">
-        <v>5.1327e-06</v>
+        <v>5.1535e-06</v>
       </c>
       <c r="O73" t="n">
-        <v>2.6692e-06</v>
+        <v>2.6808e-06</v>
       </c>
       <c r="P73" t="n">
-        <v>5.1327e-06</v>
+        <v>5.1535e-06</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.9018e-07</v>
+        <v>1.9081e-07</v>
       </c>
       <c r="R73" t="n">
-        <v>9.4207e-08</v>
+        <v>9.447700000000001e-08</v>
       </c>
       <c r="S73" t="n">
-        <v>2.8439e-07</v>
+        <v>2.8529e-07</v>
       </c>
       <c r="T73" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U73" t="n">
-        <v>12.44296407699585</v>
+        <v>12.43495082855225</v>
       </c>
     </row>
     <row r="74">
@@ -5530,46 +5530,46 @@
         <v>0.02</v>
       </c>
       <c r="H74" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I74" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>76926</v>
+        <v>76803</v>
       </c>
       <c r="L74" t="n">
-        <v>102568</v>
+        <v>102404</v>
       </c>
       <c r="M74" t="n">
-        <v>179494</v>
+        <v>179207</v>
       </c>
       <c r="N74" t="n">
-        <v>1.8741e-05</v>
+        <v>1.9402e-05</v>
       </c>
       <c r="O74" t="n">
-        <v>2.0288e-05</v>
+        <v>2.0955e-05</v>
       </c>
       <c r="P74" t="n">
-        <v>2.0288e-05</v>
+        <v>2.0955e-05</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.2122e-06</v>
+        <v>1.2537e-06</v>
       </c>
       <c r="R74" t="n">
-        <v>1.2507e-06</v>
+        <v>1.2923e-06</v>
       </c>
       <c r="S74" t="n">
-        <v>2.4629e-06</v>
+        <v>2.546e-06</v>
       </c>
       <c r="T74" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U74" t="n">
-        <v>14.87514495849609</v>
+        <v>14.85086894035339</v>
       </c>
     </row>
     <row r="75">
@@ -5599,46 +5599,46 @@
         <v>0.02</v>
       </c>
       <c r="H75" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I75" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>76926</v>
+        <v>76803</v>
       </c>
       <c r="L75" t="n">
-        <v>102568</v>
+        <v>102404</v>
       </c>
       <c r="M75" t="n">
-        <v>179494</v>
+        <v>179207</v>
       </c>
       <c r="N75" t="n">
-        <v>1.6692e-07</v>
+        <v>1.7003e-07</v>
       </c>
       <c r="O75" t="n">
-        <v>7.908299999999999e-08</v>
+        <v>8.0516e-08</v>
       </c>
       <c r="P75" t="n">
-        <v>1.6692e-07</v>
+        <v>1.7003e-07</v>
       </c>
       <c r="Q75" t="n">
-        <v>5.7146e-09</v>
+        <v>5.7813e-09</v>
       </c>
       <c r="R75" t="n">
-        <v>4.221e-09</v>
+        <v>4.3177e-09</v>
       </c>
       <c r="S75" t="n">
-        <v>9.9356e-09</v>
+        <v>1.0099e-08</v>
       </c>
       <c r="T75" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U75" t="n">
-        <v>8.146173238754272</v>
+        <v>8.15451979637146</v>
       </c>
     </row>
     <row r="76">
@@ -5668,46 +5668,46 @@
         <v>0.02</v>
       </c>
       <c r="H76" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I76" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>102568</v>
+        <v>102404</v>
       </c>
       <c r="L76" t="n">
-        <v>230778</v>
+        <v>230409</v>
       </c>
       <c r="M76" t="n">
-        <v>333346</v>
+        <v>332813</v>
       </c>
       <c r="N76" t="n">
-        <v>3.3359e-07</v>
+        <v>3.3658e-07</v>
       </c>
       <c r="O76" t="n">
-        <v>2.0249e-07</v>
+        <v>2.0426e-07</v>
       </c>
       <c r="P76" t="n">
-        <v>3.3359e-07</v>
+        <v>3.3658e-07</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.2432e-08</v>
+        <v>1.2467e-08</v>
       </c>
       <c r="R76" t="n">
-        <v>6.2525e-09</v>
+        <v>6.2899e-09</v>
       </c>
       <c r="S76" t="n">
-        <v>1.8684e-08</v>
+        <v>1.8757e-08</v>
       </c>
       <c r="T76" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U76" t="n">
-        <v>9.537918090820312</v>
+        <v>10.16196799278259</v>
       </c>
     </row>
     <row r="77">
@@ -5737,46 +5737,46 @@
         <v>0.01</v>
       </c>
       <c r="H77" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I77" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>51284</v>
+        <v>51202</v>
       </c>
       <c r="L77" t="n">
-        <v>76926</v>
+        <v>76803</v>
       </c>
       <c r="M77" t="n">
-        <v>128210</v>
+        <v>128005</v>
       </c>
       <c r="N77" t="n">
-        <v>5.6801e-05</v>
+        <v>5.7542e-05</v>
       </c>
       <c r="O77" t="n">
-        <v>0.00011675</v>
+        <v>0.00011949</v>
       </c>
       <c r="P77" t="n">
-        <v>0.00011675</v>
+        <v>0.00011949</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.9528e-06</v>
+        <v>2.0023e-06</v>
       </c>
       <c r="R77" t="n">
-        <v>3.0109e-06</v>
+        <v>3.0882e-06</v>
       </c>
       <c r="S77" t="n">
-        <v>4.9636e-06</v>
+        <v>5.0905e-06</v>
       </c>
       <c r="T77" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U77" t="n">
-        <v>11.62767100334167</v>
+        <v>11.59808421134949</v>
       </c>
     </row>
     <row r="78">
@@ -5806,46 +5806,46 @@
         <v>0.01</v>
       </c>
       <c r="H78" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I78" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>76926</v>
+        <v>76803</v>
       </c>
       <c r="L78" t="n">
-        <v>102568</v>
+        <v>102404</v>
       </c>
       <c r="M78" t="n">
-        <v>179494</v>
+        <v>179207</v>
       </c>
       <c r="N78" t="n">
-        <v>3.7452e-05</v>
+        <v>3.757e-05</v>
       </c>
       <c r="O78" t="n">
-        <v>1.8743e-05</v>
+        <v>1.8802e-05</v>
       </c>
       <c r="P78" t="n">
-        <v>3.7452e-05</v>
+        <v>3.757e-05</v>
       </c>
       <c r="Q78" t="n">
-        <v>8.5488e-07</v>
+        <v>8.5751e-07</v>
       </c>
       <c r="R78" t="n">
-        <v>4.3058e-07</v>
+        <v>4.32e-07</v>
       </c>
       <c r="S78" t="n">
-        <v>1.2855e-06</v>
+        <v>1.2895e-06</v>
       </c>
       <c r="T78" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U78" t="n">
-        <v>12.3359649181366</v>
+        <v>12.36663508415222</v>
       </c>
     </row>
     <row r="79">
@@ -5875,46 +5875,46 @@
         <v>0.01</v>
       </c>
       <c r="H79" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I79" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>76926</v>
+        <v>76803</v>
       </c>
       <c r="L79" t="n">
-        <v>102568</v>
+        <v>102404</v>
       </c>
       <c r="M79" t="n">
-        <v>179494</v>
+        <v>179207</v>
       </c>
       <c r="N79" t="n">
-        <v>3.1807e-05</v>
+        <v>3.3158e-05</v>
       </c>
       <c r="O79" t="n">
-        <v>4.5682e-05</v>
+        <v>4.7076e-05</v>
       </c>
       <c r="P79" t="n">
-        <v>4.5682e-05</v>
+        <v>4.7076e-05</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.1374e-06</v>
+        <v>1.1779e-06</v>
       </c>
       <c r="R79" t="n">
-        <v>1.3084e-06</v>
+        <v>1.35e-06</v>
       </c>
       <c r="S79" t="n">
-        <v>2.4457e-06</v>
+        <v>2.5279e-06</v>
       </c>
       <c r="T79" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U79" t="n">
-        <v>14.88466596603394</v>
+        <v>14.81956005096436</v>
       </c>
     </row>
     <row r="80">
@@ -5944,46 +5944,46 @@
         <v>0.01</v>
       </c>
       <c r="H80" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I80" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>76926</v>
+        <v>76803</v>
       </c>
       <c r="L80" t="n">
-        <v>102568</v>
+        <v>102404</v>
       </c>
       <c r="M80" t="n">
-        <v>179494</v>
+        <v>179207</v>
       </c>
       <c r="N80" t="n">
-        <v>2.2988e-07</v>
+        <v>2.3951e-07</v>
       </c>
       <c r="O80" t="n">
-        <v>3.4062e-07</v>
+        <v>3.5115e-07</v>
       </c>
       <c r="P80" t="n">
-        <v>3.4062e-07</v>
+        <v>3.5115e-07</v>
       </c>
       <c r="Q80" t="n">
-        <v>7.7589e-09</v>
+        <v>7.939399999999999e-09</v>
       </c>
       <c r="R80" t="n">
-        <v>7.879799999999999e-09</v>
+        <v>8.096500000000001e-09</v>
       </c>
       <c r="S80" t="n">
-        <v>1.5639e-08</v>
+        <v>1.6036e-08</v>
       </c>
       <c r="T80" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U80" t="n">
-        <v>7.761529922485352</v>
+        <v>7.747721910476685</v>
       </c>
     </row>
     <row r="81">
@@ -6013,46 +6013,46 @@
         <v>0.01</v>
       </c>
       <c r="H81" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="I81" t="n">
-        <v>25642</v>
+        <v>25601</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>102568</v>
+        <v>102404</v>
       </c>
       <c r="L81" t="n">
-        <v>230778</v>
+        <v>230409</v>
       </c>
       <c r="M81" t="n">
-        <v>333346</v>
+        <v>332813</v>
       </c>
       <c r="N81" t="n">
-        <v>1.9307e-06</v>
+        <v>1.9361e-06</v>
       </c>
       <c r="O81" t="n">
-        <v>9.9753e-07</v>
+        <v>1.0061e-06</v>
       </c>
       <c r="P81" t="n">
-        <v>1.9307e-06</v>
+        <v>1.9361e-06</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.5434e-08</v>
+        <v>4.5603e-08</v>
       </c>
       <c r="R81" t="n">
-        <v>2.254e-08</v>
+        <v>2.2668e-08</v>
       </c>
       <c r="S81" t="n">
-        <v>6.7975e-08</v>
+        <v>6.8271e-08</v>
       </c>
       <c r="T81" t="n">
-        <v>3.899851805631386e-05</v>
+        <v>3.906097418069607e-05</v>
       </c>
       <c r="U81" t="n">
-        <v>9.007995843887329</v>
+        <v>9.635751962661743</v>
       </c>
     </row>
     <row r="82">
@@ -6082,46 +6082,46 @@
         <v>0.1</v>
       </c>
       <c r="H82" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I82" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>25642</v>
+        <v>25600</v>
       </c>
       <c r="L82" t="n">
-        <v>38463</v>
+        <v>38400</v>
       </c>
       <c r="M82" t="n">
-        <v>64105</v>
+        <v>64000</v>
       </c>
       <c r="N82" t="n">
-        <v>1.492e-05</v>
+        <v>3.1009e-05</v>
       </c>
       <c r="O82" t="n">
-        <v>1.5088e-05</v>
+        <v>3.1223e-05</v>
       </c>
       <c r="P82" t="n">
-        <v>1.5088e-05</v>
+        <v>3.1223e-05</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.5888e-06</v>
+        <v>7.5047e-06</v>
       </c>
       <c r="R82" t="n">
-        <v>3.6601e-06</v>
+        <v>7.5766e-06</v>
       </c>
       <c r="S82" t="n">
-        <v>7.249e-06</v>
+        <v>1.5081e-05</v>
       </c>
       <c r="T82" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U82" t="n">
-        <v>5.83310079574585</v>
+        <v>5.812995195388794</v>
       </c>
     </row>
     <row r="83">
@@ -6151,46 +6151,46 @@
         <v>0.1</v>
       </c>
       <c r="H83" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I83" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>38463</v>
+        <v>38400</v>
       </c>
       <c r="L83" t="n">
-        <v>51284</v>
+        <v>51200</v>
       </c>
       <c r="M83" t="n">
-        <v>89747</v>
+        <v>89600</v>
       </c>
       <c r="N83" t="n">
-        <v>2.2758e-07</v>
+        <v>2.4531e-07</v>
       </c>
       <c r="O83" t="n">
-        <v>1.2119e-07</v>
+        <v>1.3013e-07</v>
       </c>
       <c r="P83" t="n">
-        <v>2.2758e-07</v>
+        <v>2.4531e-07</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.7185e-08</v>
+        <v>3.8829e-08</v>
       </c>
       <c r="R83" t="n">
-        <v>1.7758e-08</v>
+        <v>1.793e-08</v>
       </c>
       <c r="S83" t="n">
-        <v>5.4944e-08</v>
+        <v>5.6759e-08</v>
       </c>
       <c r="T83" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U83" t="n">
-        <v>6.751892805099487</v>
+        <v>6.761763095855713</v>
       </c>
     </row>
     <row r="84">
@@ -6220,46 +6220,46 @@
         <v>0.1</v>
       </c>
       <c r="H84" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I84" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>38463</v>
+        <v>38400</v>
       </c>
       <c r="L84" t="n">
-        <v>51284</v>
+        <v>51200</v>
       </c>
       <c r="M84" t="n">
-        <v>89747</v>
+        <v>89600</v>
       </c>
       <c r="N84" t="n">
-        <v>8.251600000000001e-06</v>
+        <v>1.6691e-05</v>
       </c>
       <c r="O84" t="n">
-        <v>8.229100000000001e-06</v>
+        <v>1.6694e-05</v>
       </c>
       <c r="P84" t="n">
-        <v>8.251600000000001e-06</v>
+        <v>1.6694e-05</v>
       </c>
       <c r="Q84" t="n">
-        <v>1.9815e-06</v>
+        <v>4.0365e-06</v>
       </c>
       <c r="R84" t="n">
-        <v>1.9911e-06</v>
+        <v>4.0464e-06</v>
       </c>
       <c r="S84" t="n">
-        <v>3.9726e-06</v>
+        <v>8.0828e-06</v>
       </c>
       <c r="T84" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U84" t="n">
-        <v>7.459254026412964</v>
+        <v>7.488631963729858</v>
       </c>
     </row>
     <row r="85">
@@ -6289,46 +6289,46 @@
         <v>0.1</v>
       </c>
       <c r="H85" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I85" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>38463</v>
+        <v>38400</v>
       </c>
       <c r="L85" t="n">
-        <v>51284</v>
+        <v>51200</v>
       </c>
       <c r="M85" t="n">
-        <v>89747</v>
+        <v>89600</v>
       </c>
       <c r="N85" t="n">
-        <v>1.1762e-07</v>
+        <v>1.2321e-07</v>
       </c>
       <c r="O85" t="n">
-        <v>5.7459e-08</v>
+        <v>7.1526e-08</v>
       </c>
       <c r="P85" t="n">
-        <v>1.1762e-07</v>
+        <v>1.2321e-07</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.1452e-08</v>
+        <v>1.2285e-08</v>
       </c>
       <c r="R85" t="n">
-        <v>5.6096e-09</v>
+        <v>6.4303e-09</v>
       </c>
       <c r="S85" t="n">
-        <v>1.7062e-08</v>
+        <v>1.8715e-08</v>
       </c>
       <c r="T85" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U85" t="n">
-        <v>5.849146127700806</v>
+        <v>5.80846905708313</v>
       </c>
     </row>
     <row r="86">
@@ -6358,46 +6358,46 @@
         <v>0.1</v>
       </c>
       <c r="H86" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I86" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>51284</v>
+        <v>51200</v>
       </c>
       <c r="L86" t="n">
-        <v>115389</v>
+        <v>115200</v>
       </c>
       <c r="M86" t="n">
-        <v>166673</v>
+        <v>166400</v>
       </c>
       <c r="N86" t="n">
-        <v>1.3421e-07</v>
+        <v>1.4794e-07</v>
       </c>
       <c r="O86" t="n">
-        <v>7.8112e-08</v>
+        <v>7.332e-08</v>
       </c>
       <c r="P86" t="n">
-        <v>1.3421e-07</v>
+        <v>1.4794e-07</v>
       </c>
       <c r="Q86" t="n">
-        <v>1.7692e-08</v>
+        <v>1.846e-08</v>
       </c>
       <c r="R86" t="n">
-        <v>9.502200000000001e-09</v>
+        <v>9.212599999999999e-09</v>
       </c>
       <c r="S86" t="n">
-        <v>2.7194e-08</v>
+        <v>2.7673e-08</v>
       </c>
       <c r="T86" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U86" t="n">
-        <v>6.959644317626953</v>
+        <v>6.976373195648193</v>
       </c>
     </row>
     <row r="87">
@@ -6427,46 +6427,46 @@
         <v>0.05</v>
       </c>
       <c r="H87" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I87" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>25642</v>
+        <v>25600</v>
       </c>
       <c r="L87" t="n">
-        <v>38463</v>
+        <v>38400</v>
       </c>
       <c r="M87" t="n">
-        <v>64105</v>
+        <v>64000</v>
       </c>
       <c r="N87" t="n">
-        <v>2.682e-05</v>
+        <v>5.7322e-05</v>
       </c>
       <c r="O87" t="n">
-        <v>2.9337e-05</v>
+        <v>5.997e-05</v>
       </c>
       <c r="P87" t="n">
-        <v>2.9337e-05</v>
+        <v>5.997e-05</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.9706e-06</v>
+        <v>8.406e-06</v>
       </c>
       <c r="R87" t="n">
-        <v>4.1959e-06</v>
+        <v>8.633e-06</v>
       </c>
       <c r="S87" t="n">
-        <v>8.166500000000001e-06</v>
+        <v>1.7039e-05</v>
       </c>
       <c r="T87" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U87" t="n">
-        <v>5.837145090103149</v>
+        <v>5.794341087341309</v>
       </c>
     </row>
     <row r="88">
@@ -6496,46 +6496,46 @@
         <v>0.05</v>
       </c>
       <c r="H88" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I88" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>38463</v>
+        <v>38400</v>
       </c>
       <c r="L88" t="n">
-        <v>51284</v>
+        <v>51200</v>
       </c>
       <c r="M88" t="n">
-        <v>89747</v>
+        <v>89600</v>
       </c>
       <c r="N88" t="n">
-        <v>1.4591e-06</v>
+        <v>1.4442e-06</v>
       </c>
       <c r="O88" t="n">
-        <v>7.635e-07</v>
+        <v>7.9268e-07</v>
       </c>
       <c r="P88" t="n">
-        <v>1.4591e-06</v>
+        <v>1.4442e-06</v>
       </c>
       <c r="Q88" t="n">
-        <v>1.2344e-07</v>
+        <v>1.2611e-07</v>
       </c>
       <c r="R88" t="n">
-        <v>5.9821e-08</v>
+        <v>5.9692e-08</v>
       </c>
       <c r="S88" t="n">
-        <v>1.8326e-07</v>
+        <v>1.858e-07</v>
       </c>
       <c r="T88" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U88" t="n">
-        <v>6.42386794090271</v>
+        <v>6.41605281829834</v>
       </c>
     </row>
     <row r="89">
@@ -6565,46 +6565,46 @@
         <v>0.05</v>
       </c>
       <c r="H89" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I89" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>38463</v>
+        <v>38400</v>
       </c>
       <c r="L89" t="n">
-        <v>51284</v>
+        <v>51200</v>
       </c>
       <c r="M89" t="n">
-        <v>89747</v>
+        <v>89600</v>
       </c>
       <c r="N89" t="n">
-        <v>1.5339e-05</v>
+        <v>3.1393e-05</v>
       </c>
       <c r="O89" t="n">
-        <v>1.5654e-05</v>
+        <v>3.1725e-05</v>
       </c>
       <c r="P89" t="n">
-        <v>1.5654e-05</v>
+        <v>3.1725e-05</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.2339e-06</v>
+        <v>4.5617e-06</v>
       </c>
       <c r="R89" t="n">
-        <v>2.2604e-06</v>
+        <v>4.5883e-06</v>
       </c>
       <c r="S89" t="n">
-        <v>4.4942e-06</v>
+        <v>9.15e-06</v>
       </c>
       <c r="T89" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U89" t="n">
-        <v>7.475862741470337</v>
+        <v>7.499217987060547</v>
       </c>
     </row>
     <row r="90">
@@ -6634,46 +6634,46 @@
         <v>0.05</v>
       </c>
       <c r="H90" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I90" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>38463</v>
+        <v>38400</v>
       </c>
       <c r="L90" t="n">
-        <v>51284</v>
+        <v>51200</v>
       </c>
       <c r="M90" t="n">
-        <v>89747</v>
+        <v>89600</v>
       </c>
       <c r="N90" t="n">
-        <v>1.3131e-07</v>
+        <v>1.7752e-07</v>
       </c>
       <c r="O90" t="n">
-        <v>7.6903e-08</v>
+        <v>1.4022e-07</v>
       </c>
       <c r="P90" t="n">
-        <v>1.3131e-07</v>
+        <v>1.7752e-07</v>
       </c>
       <c r="Q90" t="n">
-        <v>9.815400000000001e-09</v>
+        <v>1.428e-08</v>
       </c>
       <c r="R90" t="n">
-        <v>5.2288e-09</v>
+        <v>9.4909e-09</v>
       </c>
       <c r="S90" t="n">
-        <v>1.5044e-08</v>
+        <v>2.3771e-08</v>
       </c>
       <c r="T90" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U90" t="n">
-        <v>4.781357765197754</v>
+        <v>4.756927967071533</v>
       </c>
     </row>
     <row r="91">
@@ -6703,46 +6703,46 @@
         <v>0.05</v>
       </c>
       <c r="H91" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I91" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>51284</v>
+        <v>51200</v>
       </c>
       <c r="L91" t="n">
-        <v>115389</v>
+        <v>115200</v>
       </c>
       <c r="M91" t="n">
-        <v>166673</v>
+        <v>166400</v>
       </c>
       <c r="N91" t="n">
-        <v>1.449e-07</v>
+        <v>1.8784e-07</v>
       </c>
       <c r="O91" t="n">
-        <v>1.1114e-07</v>
+        <v>1.4674e-07</v>
       </c>
       <c r="P91" t="n">
-        <v>1.449e-07</v>
+        <v>1.8784e-07</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.0129e-08</v>
+        <v>1.4946e-08</v>
       </c>
       <c r="R91" t="n">
-        <v>9.1174e-09</v>
+        <v>1.0098e-08</v>
       </c>
       <c r="S91" t="n">
-        <v>1.9246e-08</v>
+        <v>2.5044e-08</v>
       </c>
       <c r="T91" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U91" t="n">
-        <v>5.617464780807495</v>
+        <v>5.628592014312744</v>
       </c>
     </row>
     <row r="92">
@@ -6772,46 +6772,46 @@
         <v>0.02</v>
       </c>
       <c r="H92" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I92" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>25642</v>
+        <v>25600</v>
       </c>
       <c r="L92" t="n">
-        <v>38463</v>
+        <v>38400</v>
       </c>
       <c r="M92" t="n">
-        <v>64105</v>
+        <v>64000</v>
       </c>
       <c r="N92" t="n">
-        <v>4.8585e-05</v>
+        <v>0.00011388</v>
       </c>
       <c r="O92" t="n">
-        <v>8.557e-05</v>
+        <v>0.00015937</v>
       </c>
       <c r="P92" t="n">
-        <v>8.557e-05</v>
+        <v>0.00015937</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.4696e-06</v>
+        <v>8.0629e-06</v>
       </c>
       <c r="R92" t="n">
-        <v>4.7356e-06</v>
+        <v>9.3422e-06</v>
       </c>
       <c r="S92" t="n">
-        <v>8.205200000000001e-06</v>
+        <v>1.7405e-05</v>
       </c>
       <c r="T92" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U92" t="n">
-        <v>5.825371026992798</v>
+        <v>5.79700779914856</v>
       </c>
     </row>
     <row r="93">
@@ -6841,46 +6841,46 @@
         <v>0.02</v>
       </c>
       <c r="H93" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I93" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>38463</v>
+        <v>38400</v>
       </c>
       <c r="L93" t="n">
-        <v>51284</v>
+        <v>51200</v>
       </c>
       <c r="M93" t="n">
-        <v>89747</v>
+        <v>89600</v>
       </c>
       <c r="N93" t="n">
-        <v>1.9794e-05</v>
+        <v>1.9986e-05</v>
       </c>
       <c r="O93" t="n">
-        <v>1.0114e-05</v>
+        <v>1.0401e-05</v>
       </c>
       <c r="P93" t="n">
-        <v>1.9794e-05</v>
+        <v>1.9986e-05</v>
       </c>
       <c r="Q93" t="n">
-        <v>7.3071e-07</v>
+        <v>7.3516e-07</v>
       </c>
       <c r="R93" t="n">
-        <v>3.6374e-07</v>
+        <v>3.6364e-07</v>
       </c>
       <c r="S93" t="n">
-        <v>1.0944e-06</v>
+        <v>1.0988e-06</v>
       </c>
       <c r="T93" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U93" t="n">
-        <v>6.213797092437744</v>
+        <v>6.197579145431519</v>
       </c>
     </row>
     <row r="94">
@@ -6910,46 +6910,46 @@
         <v>0.02</v>
       </c>
       <c r="H94" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I94" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>38463</v>
+        <v>38400</v>
       </c>
       <c r="L94" t="n">
-        <v>51284</v>
+        <v>51200</v>
       </c>
       <c r="M94" t="n">
-        <v>89747</v>
+        <v>89600</v>
       </c>
       <c r="N94" t="n">
-        <v>3.3676e-05</v>
+        <v>7.211999999999999e-05</v>
       </c>
       <c r="O94" t="n">
-        <v>3.945e-05</v>
+        <v>7.8166e-05</v>
       </c>
       <c r="P94" t="n">
-        <v>3.945e-05</v>
+        <v>7.8166e-05</v>
       </c>
       <c r="Q94" t="n">
-        <v>2.243e-06</v>
+        <v>4.6658e-06</v>
       </c>
       <c r="R94" t="n">
-        <v>2.3951e-06</v>
+        <v>4.8181e-06</v>
       </c>
       <c r="S94" t="n">
-        <v>4.6381e-06</v>
+        <v>9.483800000000001e-06</v>
       </c>
       <c r="T94" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U94" t="n">
-        <v>7.450050115585327</v>
+        <v>7.475594997406006</v>
       </c>
     </row>
     <row r="95">
@@ -6979,46 +6979,46 @@
         <v>0.02</v>
       </c>
       <c r="H95" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I95" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>38463</v>
+        <v>38400</v>
       </c>
       <c r="L95" t="n">
-        <v>51284</v>
+        <v>51200</v>
       </c>
       <c r="M95" t="n">
-        <v>89747</v>
+        <v>89600</v>
       </c>
       <c r="N95" t="n">
-        <v>2.9655e-07</v>
+        <v>7.0189e-07</v>
       </c>
       <c r="O95" t="n">
-        <v>2.6035e-07</v>
+        <v>6.5467e-07</v>
       </c>
       <c r="P95" t="n">
-        <v>2.9655e-07</v>
+        <v>7.0189e-07</v>
       </c>
       <c r="Q95" t="n">
-        <v>9.822e-09</v>
+        <v>2.289e-08</v>
       </c>
       <c r="R95" t="n">
-        <v>1.0251e-08</v>
+        <v>2.342e-08</v>
       </c>
       <c r="S95" t="n">
-        <v>2.0073e-08</v>
+        <v>4.631e-08</v>
       </c>
       <c r="T95" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U95" t="n">
-        <v>4.118619918823242</v>
+        <v>4.132138967514038</v>
       </c>
     </row>
     <row r="96">
@@ -7048,46 +7048,46 @@
         <v>0.02</v>
       </c>
       <c r="H96" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I96" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>51284</v>
+        <v>51200</v>
       </c>
       <c r="L96" t="n">
-        <v>115389</v>
+        <v>115200</v>
       </c>
       <c r="M96" t="n">
-        <v>166673</v>
+        <v>166400</v>
       </c>
       <c r="N96" t="n">
-        <v>4.0043e-07</v>
+        <v>8.3385e-07</v>
       </c>
       <c r="O96" t="n">
-        <v>2.5226e-07</v>
+        <v>6.779e-07</v>
       </c>
       <c r="P96" t="n">
-        <v>4.0043e-07</v>
+        <v>8.3385e-07</v>
       </c>
       <c r="Q96" t="n">
-        <v>1.2408e-08</v>
+        <v>2.6431e-08</v>
       </c>
       <c r="R96" t="n">
-        <v>1.0143e-08</v>
+        <v>2.4293e-08</v>
       </c>
       <c r="S96" t="n">
-        <v>2.255e-08</v>
+        <v>5.0724e-08</v>
       </c>
       <c r="T96" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U96" t="n">
-        <v>4.810128211975098</v>
+        <v>4.841552019119263</v>
       </c>
     </row>
     <row r="97">
@@ -7117,46 +7117,46 @@
         <v>0.01</v>
       </c>
       <c r="H97" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I97" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>25642</v>
+        <v>25600</v>
       </c>
       <c r="L97" t="n">
-        <v>38463</v>
+        <v>38400</v>
       </c>
       <c r="M97" t="n">
-        <v>64105</v>
+        <v>64000</v>
       </c>
       <c r="N97" t="n">
-        <v>0.0001904</v>
+        <v>0.00022158</v>
       </c>
       <c r="O97" t="n">
-        <v>0.00029501</v>
+        <v>0.00044859</v>
       </c>
       <c r="P97" t="n">
-        <v>0.00029501</v>
+        <v>0.00044859</v>
       </c>
       <c r="Q97" t="n">
-        <v>6.6194e-06</v>
+        <v>7.532e-06</v>
       </c>
       <c r="R97" t="n">
-        <v>7.2167e-06</v>
+        <v>1.1528e-05</v>
       </c>
       <c r="S97" t="n">
-        <v>1.3836e-05</v>
+        <v>1.906e-05</v>
       </c>
       <c r="T97" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U97" t="n">
-        <v>5.827639102935791</v>
+        <v>5.789817094802856</v>
       </c>
     </row>
     <row r="98">
@@ -7186,46 +7186,46 @@
         <v>0.01</v>
       </c>
       <c r="H98" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I98" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>38463</v>
+        <v>38400</v>
       </c>
       <c r="L98" t="n">
-        <v>51284</v>
+        <v>51200</v>
       </c>
       <c r="M98" t="n">
-        <v>89747</v>
+        <v>89600</v>
       </c>
       <c r="N98" t="n">
-        <v>0.00014539</v>
+        <v>0.00014591</v>
       </c>
       <c r="O98" t="n">
-        <v>7.2783e-05</v>
+        <v>7.2996e-05</v>
       </c>
       <c r="P98" t="n">
-        <v>0.00014539</v>
+        <v>0.00014591</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.3176e-06</v>
+        <v>3.3242e-06</v>
       </c>
       <c r="R98" t="n">
-        <v>1.6651e-06</v>
+        <v>1.6752e-06</v>
       </c>
       <c r="S98" t="n">
-        <v>4.9827e-06</v>
+        <v>4.9994e-06</v>
       </c>
       <c r="T98" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U98" t="n">
-        <v>6.15715503692627</v>
+        <v>6.127299070358276</v>
       </c>
     </row>
     <row r="99">
@@ -7255,46 +7255,46 @@
         <v>0.01</v>
       </c>
       <c r="H99" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I99" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>38463</v>
+        <v>38400</v>
       </c>
       <c r="L99" t="n">
-        <v>51284</v>
+        <v>51200</v>
       </c>
       <c r="M99" t="n">
-        <v>89747</v>
+        <v>89600</v>
       </c>
       <c r="N99" t="n">
-        <v>4.6705e-05</v>
+        <v>0.00012197</v>
       </c>
       <c r="O99" t="n">
-        <v>9.577900000000001e-05</v>
+        <v>0.00017622</v>
       </c>
       <c r="P99" t="n">
-        <v>9.577900000000001e-05</v>
+        <v>0.00017622</v>
       </c>
       <c r="Q99" t="n">
-        <v>2.0401e-06</v>
+        <v>4.3753e-06</v>
       </c>
       <c r="R99" t="n">
-        <v>2.6325e-06</v>
+        <v>5.0435e-06</v>
       </c>
       <c r="S99" t="n">
-        <v>4.6726e-06</v>
+        <v>9.4188e-06</v>
       </c>
       <c r="T99" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U99" t="n">
-        <v>7.46220588684082</v>
+        <v>7.476243257522583</v>
       </c>
     </row>
     <row r="100">
@@ -7324,46 +7324,46 @@
         <v>0.01</v>
       </c>
       <c r="H100" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I100" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>38463</v>
+        <v>38400</v>
       </c>
       <c r="L100" t="n">
-        <v>51284</v>
+        <v>51200</v>
       </c>
       <c r="M100" t="n">
-        <v>89747</v>
+        <v>89600</v>
       </c>
       <c r="N100" t="n">
-        <v>3.6063e-07</v>
+        <v>1.6763e-06</v>
       </c>
       <c r="O100" t="n">
-        <v>1.1372e-06</v>
+        <v>2.4792e-06</v>
       </c>
       <c r="P100" t="n">
-        <v>1.1372e-06</v>
+        <v>2.4792e-06</v>
       </c>
       <c r="Q100" t="n">
-        <v>1.4101e-08</v>
+        <v>3.7616e-08</v>
       </c>
       <c r="R100" t="n">
-        <v>2.5706e-08</v>
+        <v>5.3402e-08</v>
       </c>
       <c r="S100" t="n">
-        <v>3.9807e-08</v>
+        <v>9.1018e-08</v>
       </c>
       <c r="T100" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U100" t="n">
-        <v>3.925230979919434</v>
+        <v>3.932744741439819</v>
       </c>
     </row>
     <row r="101">
@@ -7393,46 +7393,46 @@
         <v>0.01</v>
       </c>
       <c r="H101" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="I101" t="n">
-        <v>12821</v>
+        <v>12800</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>51284</v>
+        <v>51200</v>
       </c>
       <c r="L101" t="n">
-        <v>115389</v>
+        <v>115200</v>
       </c>
       <c r="M101" t="n">
-        <v>166673</v>
+        <v>166400</v>
       </c>
       <c r="N101" t="n">
-        <v>1.3352e-06</v>
+        <v>2.745e-06</v>
       </c>
       <c r="O101" t="n">
-        <v>8.7426e-07</v>
+        <v>2.3272e-06</v>
       </c>
       <c r="P101" t="n">
-        <v>1.3352e-06</v>
+        <v>2.745e-06</v>
       </c>
       <c r="Q101" t="n">
-        <v>2.9608e-08</v>
+        <v>5.9518e-08</v>
       </c>
       <c r="R101" t="n">
-        <v>1.8157e-08</v>
+        <v>4.7754e-08</v>
       </c>
       <c r="S101" t="n">
-        <v>4.7764e-08</v>
+        <v>1.0727e-07</v>
       </c>
       <c r="T101" t="n">
-        <v>7.799703611262772e-05</v>
+        <v>7.8125e-05</v>
       </c>
       <c r="U101" t="n">
-        <v>4.515569925308228</v>
+        <v>4.551133871078491</v>
       </c>
     </row>
     <row r="102">
@@ -7462,46 +7462,46 @@
         <v>0.1</v>
       </c>
       <c r="H102" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I102" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>12822</v>
+        <v>12802</v>
       </c>
       <c r="L102" t="n">
-        <v>19233</v>
+        <v>19203</v>
       </c>
       <c r="M102" t="n">
-        <v>32055</v>
+        <v>32005</v>
       </c>
       <c r="N102" t="n">
-        <v>3.5258e-05</v>
+        <v>0.00010606</v>
       </c>
       <c r="O102" t="n">
-        <v>3.6046e-05</v>
+        <v>0.00010694</v>
       </c>
       <c r="P102" t="n">
-        <v>3.6046e-05</v>
+        <v>0.00010694</v>
       </c>
       <c r="Q102" t="n">
-        <v>8.485600000000001e-06</v>
+        <v>2.5689e-05</v>
       </c>
       <c r="R102" t="n">
-        <v>8.7612e-06</v>
+        <v>2.5968e-05</v>
       </c>
       <c r="S102" t="n">
-        <v>1.7247e-05</v>
+        <v>5.1657e-05</v>
       </c>
       <c r="T102" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U102" t="n">
-        <v>2.943998098373413</v>
+        <v>2.931404829025269</v>
       </c>
     </row>
     <row r="103">
@@ -7531,46 +7531,46 @@
         <v>0.1</v>
       </c>
       <c r="H103" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I103" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>19233</v>
+        <v>19203</v>
       </c>
       <c r="L103" t="n">
-        <v>25644</v>
+        <v>25604</v>
       </c>
       <c r="M103" t="n">
-        <v>44877</v>
+        <v>44807</v>
       </c>
       <c r="N103" t="n">
-        <v>8.2561e-07</v>
+        <v>8.221e-07</v>
       </c>
       <c r="O103" t="n">
-        <v>4.2142e-07</v>
+        <v>4.5813e-07</v>
       </c>
       <c r="P103" t="n">
-        <v>8.2561e-07</v>
+        <v>8.221e-07</v>
       </c>
       <c r="Q103" t="n">
-        <v>1.3014e-07</v>
+        <v>1.3838e-07</v>
       </c>
       <c r="R103" t="n">
-        <v>6.1755e-08</v>
+        <v>6.2191e-08</v>
       </c>
       <c r="S103" t="n">
-        <v>1.919e-07</v>
+        <v>2.0057e-07</v>
       </c>
       <c r="T103" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U103" t="n">
-        <v>3.514520645141602</v>
+        <v>3.531996965408325</v>
       </c>
     </row>
     <row r="104">
@@ -7600,46 +7600,46 @@
         <v>0.1</v>
       </c>
       <c r="H104" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I104" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>19233</v>
+        <v>19203</v>
       </c>
       <c r="L104" t="n">
-        <v>25644</v>
+        <v>25604</v>
       </c>
       <c r="M104" t="n">
-        <v>44877</v>
+        <v>44807</v>
       </c>
       <c r="N104" t="n">
-        <v>1.9857e-05</v>
+        <v>5.6361e-05</v>
       </c>
       <c r="O104" t="n">
-        <v>1.9931e-05</v>
+        <v>5.6499e-05</v>
       </c>
       <c r="P104" t="n">
-        <v>1.9931e-05</v>
+        <v>5.6499e-05</v>
       </c>
       <c r="Q104" t="n">
-        <v>4.7985e-06</v>
+        <v>1.3676e-05</v>
       </c>
       <c r="R104" t="n">
-        <v>4.8343e-06</v>
+        <v>1.3713e-05</v>
       </c>
       <c r="S104" t="n">
-        <v>9.6328e-06</v>
+        <v>2.7388e-05</v>
       </c>
       <c r="T104" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U104" t="n">
-        <v>3.771072149276733</v>
+        <v>3.750862836837769</v>
       </c>
     </row>
     <row r="105">
@@ -7669,46 +7669,46 @@
         <v>0.1</v>
       </c>
       <c r="H105" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I105" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>19233</v>
+        <v>19203</v>
       </c>
       <c r="L105" t="n">
-        <v>25644</v>
+        <v>25604</v>
       </c>
       <c r="M105" t="n">
-        <v>44877</v>
+        <v>44807</v>
       </c>
       <c r="N105" t="n">
-        <v>1.3242e-07</v>
+        <v>2.0984e-07</v>
       </c>
       <c r="O105" t="n">
-        <v>1.0001e-07</v>
+        <v>2.2628e-07</v>
       </c>
       <c r="P105" t="n">
-        <v>1.3242e-07</v>
+        <v>2.2628e-07</v>
       </c>
       <c r="Q105" t="n">
-        <v>1.4381e-08</v>
+        <v>3.0776e-08</v>
       </c>
       <c r="R105" t="n">
-        <v>9.235299999999999e-09</v>
+        <v>2.6506e-08</v>
       </c>
       <c r="S105" t="n">
-        <v>2.3616e-08</v>
+        <v>5.7283e-08</v>
       </c>
       <c r="T105" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U105" t="n">
-        <v>3.304681301116943</v>
+        <v>3.308987855911255</v>
       </c>
     </row>
     <row r="106">
@@ -7738,46 +7738,46 @@
         <v>0.1</v>
       </c>
       <c r="H106" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I106" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>25644</v>
+        <v>25604</v>
       </c>
       <c r="L106" t="n">
-        <v>57699</v>
+        <v>57609</v>
       </c>
       <c r="M106" t="n">
-        <v>83343</v>
+        <v>83213</v>
       </c>
       <c r="N106" t="n">
-        <v>3.0688e-07</v>
+        <v>4.1461e-07</v>
       </c>
       <c r="O106" t="n">
-        <v>1.5286e-07</v>
+        <v>2.6157e-07</v>
       </c>
       <c r="P106" t="n">
-        <v>3.0688e-07</v>
+        <v>4.1461e-07</v>
       </c>
       <c r="Q106" t="n">
-        <v>4.2827e-08</v>
+        <v>5.5962e-08</v>
       </c>
       <c r="R106" t="n">
-        <v>2.3017e-08</v>
+        <v>3.5621e-08</v>
       </c>
       <c r="S106" t="n">
-        <v>6.5844e-08</v>
+        <v>9.158200000000001e-08</v>
       </c>
       <c r="T106" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U106" t="n">
-        <v>4.11008620262146</v>
+        <v>4.111624240875244</v>
       </c>
     </row>
     <row r="107">
@@ -7807,46 +7807,46 @@
         <v>0.05</v>
       </c>
       <c r="H107" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I107" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>12822</v>
+        <v>12802</v>
       </c>
       <c r="L107" t="n">
-        <v>19233</v>
+        <v>19203</v>
       </c>
       <c r="M107" t="n">
-        <v>32055</v>
+        <v>32005</v>
       </c>
       <c r="N107" t="n">
-        <v>6.1636e-05</v>
+        <v>0.00019562</v>
       </c>
       <c r="O107" t="n">
-        <v>7.131000000000001e-05</v>
+        <v>0.0002059</v>
       </c>
       <c r="P107" t="n">
-        <v>7.131000000000001e-05</v>
+        <v>0.0002059</v>
       </c>
       <c r="Q107" t="n">
-        <v>9.2464e-06</v>
+        <v>2.8732e-05</v>
       </c>
       <c r="R107" t="n">
-        <v>1.0123e-05</v>
+        <v>2.9618e-05</v>
       </c>
       <c r="S107" t="n">
-        <v>1.9369e-05</v>
+        <v>5.835e-05</v>
       </c>
       <c r="T107" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U107" t="n">
-        <v>2.945333957672119</v>
+        <v>2.942596912384033</v>
       </c>
     </row>
     <row r="108">
@@ -7876,46 +7876,46 @@
         <v>0.05</v>
       </c>
       <c r="H108" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I108" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>19233</v>
+        <v>19203</v>
       </c>
       <c r="L108" t="n">
-        <v>25644</v>
+        <v>25604</v>
       </c>
       <c r="M108" t="n">
-        <v>44877</v>
+        <v>44807</v>
       </c>
       <c r="N108" t="n">
-        <v>5.588e-06</v>
+        <v>5.5279e-06</v>
       </c>
       <c r="O108" t="n">
-        <v>2.8638e-06</v>
+        <v>3.0167e-06</v>
       </c>
       <c r="P108" t="n">
-        <v>5.588e-06</v>
+        <v>5.5279e-06</v>
       </c>
       <c r="Q108" t="n">
-        <v>4.7198e-07</v>
+        <v>4.86e-07</v>
       </c>
       <c r="R108" t="n">
-        <v>2.3039e-07</v>
+        <v>2.2878e-07</v>
       </c>
       <c r="S108" t="n">
-        <v>7.0236e-07</v>
+        <v>7.1478e-07</v>
       </c>
       <c r="T108" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U108" t="n">
-        <v>3.36980414390564</v>
+        <v>3.395843029022217</v>
       </c>
     </row>
     <row r="109">
@@ -7945,46 +7945,46 @@
         <v>0.05</v>
       </c>
       <c r="H109" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I109" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>19233</v>
+        <v>19203</v>
       </c>
       <c r="L109" t="n">
-        <v>25644</v>
+        <v>25604</v>
       </c>
       <c r="M109" t="n">
-        <v>44877</v>
+        <v>44807</v>
       </c>
       <c r="N109" t="n">
-        <v>3.6911e-05</v>
+        <v>0.0001063</v>
       </c>
       <c r="O109" t="n">
-        <v>3.812e-05</v>
+        <v>0.00010754</v>
       </c>
       <c r="P109" t="n">
-        <v>3.812e-05</v>
+        <v>0.00010754</v>
       </c>
       <c r="Q109" t="n">
-        <v>5.3935e-06</v>
+        <v>1.5449e-05</v>
       </c>
       <c r="R109" t="n">
-        <v>5.4965e-06</v>
+        <v>1.5553e-05</v>
       </c>
       <c r="S109" t="n">
-        <v>1.089e-05</v>
+        <v>3.1002e-05</v>
       </c>
       <c r="T109" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U109" t="n">
-        <v>3.764776945114136</v>
+        <v>3.738095760345459</v>
       </c>
     </row>
     <row r="110">
@@ -8014,46 +8014,46 @@
         <v>0.05</v>
       </c>
       <c r="H110" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I110" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>19233</v>
+        <v>19203</v>
       </c>
       <c r="L110" t="n">
-        <v>25644</v>
+        <v>25604</v>
       </c>
       <c r="M110" t="n">
-        <v>44877</v>
+        <v>44807</v>
       </c>
       <c r="N110" t="n">
-        <v>2.6504e-07</v>
+        <v>7.3965e-07</v>
       </c>
       <c r="O110" t="n">
-        <v>2.5245e-07</v>
+        <v>7.3629e-07</v>
       </c>
       <c r="P110" t="n">
-        <v>2.6504e-07</v>
+        <v>7.3965e-07</v>
       </c>
       <c r="Q110" t="n">
-        <v>2.2251e-08</v>
+        <v>6.2538e-08</v>
       </c>
       <c r="R110" t="n">
-        <v>1.8474e-08</v>
+        <v>5.8967e-08</v>
       </c>
       <c r="S110" t="n">
-        <v>4.0725e-08</v>
+        <v>1.2151e-07</v>
       </c>
       <c r="T110" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U110" t="n">
-        <v>2.966485023498535</v>
+        <v>3.001036643981934</v>
       </c>
     </row>
     <row r="111">
@@ -8083,46 +8083,46 @@
         <v>0.05</v>
       </c>
       <c r="H111" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I111" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>25644</v>
+        <v>25604</v>
       </c>
       <c r="L111" t="n">
-        <v>57699</v>
+        <v>57609</v>
       </c>
       <c r="M111" t="n">
-        <v>83343</v>
+        <v>83213</v>
       </c>
       <c r="N111" t="n">
-        <v>1.8738e-06</v>
+        <v>2.173e-06</v>
       </c>
       <c r="O111" t="n">
-        <v>1.0216e-06</v>
+        <v>1.3088e-06</v>
       </c>
       <c r="P111" t="n">
-        <v>1.8738e-06</v>
+        <v>2.173e-06</v>
       </c>
       <c r="Q111" t="n">
-        <v>1.6271e-07</v>
+        <v>1.7931e-07</v>
       </c>
       <c r="R111" t="n">
-        <v>7.928099999999999e-08</v>
+        <v>1.0042e-07</v>
       </c>
       <c r="S111" t="n">
-        <v>2.4199e-07</v>
+        <v>2.7973e-07</v>
       </c>
       <c r="T111" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U111" t="n">
-        <v>3.734021186828613</v>
+        <v>3.742498159408569</v>
       </c>
     </row>
     <row r="112">
@@ -8152,46 +8152,46 @@
         <v>0.02</v>
       </c>
       <c r="H112" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I112" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>12822</v>
+        <v>12802</v>
       </c>
       <c r="L112" t="n">
-        <v>19233</v>
+        <v>19203</v>
       </c>
       <c r="M112" t="n">
-        <v>32055</v>
+        <v>32005</v>
       </c>
       <c r="N112" t="n">
-        <v>0.00011628</v>
+        <v>0.00038118</v>
       </c>
       <c r="O112" t="n">
-        <v>0.00023312</v>
+        <v>0.0005542</v>
       </c>
       <c r="P112" t="n">
-        <v>0.00023312</v>
+        <v>0.0005542</v>
       </c>
       <c r="Q112" t="n">
-        <v>7.894600000000001e-06</v>
+        <v>2.7228e-05</v>
       </c>
       <c r="R112" t="n">
-        <v>1.2036e-05</v>
+        <v>3.222e-05</v>
       </c>
       <c r="S112" t="n">
-        <v>1.9931e-05</v>
+        <v>5.9449e-05</v>
       </c>
       <c r="T112" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U112" t="n">
-        <v>2.948461771011353</v>
+        <v>2.934337854385376</v>
       </c>
     </row>
     <row r="113">
@@ -8221,46 +8221,46 @@
         <v>0.02</v>
       </c>
       <c r="H113" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I113" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>19233</v>
+        <v>19203</v>
       </c>
       <c r="L113" t="n">
-        <v>25644</v>
+        <v>25604</v>
       </c>
       <c r="M113" t="n">
-        <v>44877</v>
+        <v>44807</v>
       </c>
       <c r="N113" t="n">
-        <v>7.6281e-05</v>
+        <v>7.713299999999999e-05</v>
       </c>
       <c r="O113" t="n">
-        <v>3.8786e-05</v>
+        <v>4.0273e-05</v>
       </c>
       <c r="P113" t="n">
-        <v>7.6281e-05</v>
+        <v>7.713299999999999e-05</v>
       </c>
       <c r="Q113" t="n">
-        <v>2.8098e-06</v>
+        <v>2.8296e-06</v>
       </c>
       <c r="R113" t="n">
-        <v>1.3998e-06</v>
+        <v>1.3972e-06</v>
       </c>
       <c r="S113" t="n">
-        <v>4.2096e-06</v>
+        <v>4.2268e-06</v>
       </c>
       <c r="T113" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U113" t="n">
-        <v>3.305170059204102</v>
+        <v>3.3123619556427</v>
       </c>
     </row>
     <row r="114">
@@ -8290,46 +8290,46 @@
         <v>0.02</v>
       </c>
       <c r="H114" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I114" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>19233</v>
+        <v>19203</v>
       </c>
       <c r="L114" t="n">
-        <v>25644</v>
+        <v>25604</v>
       </c>
       <c r="M114" t="n">
-        <v>44877</v>
+        <v>44807</v>
       </c>
       <c r="N114" t="n">
-        <v>7.781200000000001e-05</v>
+        <v>0.00024258</v>
       </c>
       <c r="O114" t="n">
-        <v>9.8558e-05</v>
+        <v>0.00026581</v>
       </c>
       <c r="P114" t="n">
-        <v>9.8558e-05</v>
+        <v>0.00026581</v>
       </c>
       <c r="Q114" t="n">
-        <v>5.2976e-06</v>
+        <v>1.5761e-05</v>
       </c>
       <c r="R114" t="n">
-        <v>5.8855e-06</v>
+        <v>1.6353e-05</v>
       </c>
       <c r="S114" t="n">
-        <v>1.1183e-05</v>
+        <v>3.2114e-05</v>
       </c>
       <c r="T114" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U114" t="n">
-        <v>3.756603956222534</v>
+        <v>3.746548891067505</v>
       </c>
     </row>
     <row r="115">
@@ -8359,46 +8359,46 @@
         <v>0.02</v>
       </c>
       <c r="H115" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I115" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>19233</v>
+        <v>19203</v>
       </c>
       <c r="L115" t="n">
-        <v>25644</v>
+        <v>25604</v>
       </c>
       <c r="M115" t="n">
-        <v>44877</v>
+        <v>44807</v>
       </c>
       <c r="N115" t="n">
-        <v>9.956499999999999e-07</v>
+        <v>4.0903e-06</v>
       </c>
       <c r="O115" t="n">
-        <v>1.5443e-06</v>
+        <v>4.6421e-06</v>
       </c>
       <c r="P115" t="n">
-        <v>1.5443e-06</v>
+        <v>4.6421e-06</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.7308e-08</v>
+        <v>1.3757e-07</v>
       </c>
       <c r="R115" t="n">
-        <v>5.0486e-08</v>
+        <v>1.5107e-07</v>
       </c>
       <c r="S115" t="n">
-        <v>8.7794e-08</v>
+        <v>2.8863e-07</v>
       </c>
       <c r="T115" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U115" t="n">
-        <v>2.768986225128174</v>
+        <v>2.806817054748535</v>
       </c>
     </row>
     <row r="116">
@@ -8428,46 +8428,46 @@
         <v>0.02</v>
       </c>
       <c r="H116" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I116" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>25644</v>
+        <v>25604</v>
       </c>
       <c r="L116" t="n">
-        <v>57699</v>
+        <v>57609</v>
       </c>
       <c r="M116" t="n">
-        <v>83343</v>
+        <v>83213</v>
       </c>
       <c r="N116" t="n">
-        <v>2.5711e-05</v>
+        <v>2.7432e-05</v>
       </c>
       <c r="O116" t="n">
-        <v>1.376e-05</v>
+        <v>1.528e-05</v>
       </c>
       <c r="P116" t="n">
-        <v>2.5711e-05</v>
+        <v>2.7432e-05</v>
       </c>
       <c r="Q116" t="n">
-        <v>9.522799999999999e-07</v>
+        <v>9.7266e-07</v>
       </c>
       <c r="R116" t="n">
-        <v>4.7219e-07</v>
+        <v>4.9433e-07</v>
       </c>
       <c r="S116" t="n">
-        <v>1.4245e-06</v>
+        <v>1.467e-06</v>
       </c>
       <c r="T116" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U116" t="n">
-        <v>3.482165098190308</v>
+        <v>3.506778001785278</v>
       </c>
     </row>
     <row r="117">
@@ -8497,46 +8497,46 @@
         <v>0.01</v>
       </c>
       <c r="H117" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I117" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>12822</v>
+        <v>12802</v>
       </c>
       <c r="L117" t="n">
-        <v>19233</v>
+        <v>19203</v>
       </c>
       <c r="M117" t="n">
-        <v>32055</v>
+        <v>32005</v>
       </c>
       <c r="N117" t="n">
-        <v>0.00085383</v>
+        <v>0.00083115</v>
       </c>
       <c r="O117" t="n">
-        <v>0.00093559</v>
+        <v>0.0016096</v>
       </c>
       <c r="P117" t="n">
-        <v>0.00093559</v>
+        <v>0.0016096</v>
       </c>
       <c r="Q117" t="n">
-        <v>2.6002e-05</v>
+        <v>2.7771e-05</v>
       </c>
       <c r="R117" t="n">
-        <v>2.2303e-05</v>
+        <v>4.097e-05</v>
       </c>
       <c r="S117" t="n">
-        <v>4.8305e-05</v>
+        <v>6.8741e-05</v>
       </c>
       <c r="T117" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U117" t="n">
-        <v>2.958800077438354</v>
+        <v>2.928295135498047</v>
       </c>
     </row>
     <row r="118">
@@ -8566,46 +8566,46 @@
         <v>0.01</v>
       </c>
       <c r="H118" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I118" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>19233</v>
+        <v>19203</v>
       </c>
       <c r="L118" t="n">
-        <v>25644</v>
+        <v>25604</v>
       </c>
       <c r="M118" t="n">
-        <v>44877</v>
+        <v>44807</v>
       </c>
       <c r="N118" t="n">
-        <v>0.0005608399999999999</v>
+        <v>0.00056297</v>
       </c>
       <c r="O118" t="n">
-        <v>0.00028074</v>
+        <v>0.00028149</v>
       </c>
       <c r="P118" t="n">
-        <v>0.0005608399999999999</v>
+        <v>0.00056297</v>
       </c>
       <c r="Q118" t="n">
-        <v>1.2784e-05</v>
+        <v>1.2804e-05</v>
       </c>
       <c r="R118" t="n">
-        <v>6.4101e-06</v>
+        <v>6.4563e-06</v>
       </c>
       <c r="S118" t="n">
-        <v>1.9195e-05</v>
+        <v>1.9261e-05</v>
       </c>
       <c r="T118" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U118" t="n">
-        <v>3.263671159744263</v>
+        <v>3.27492880821228</v>
       </c>
     </row>
     <row r="119">
@@ -8635,46 +8635,46 @@
         <v>0.01</v>
       </c>
       <c r="H119" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I119" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>19233</v>
+        <v>19203</v>
       </c>
       <c r="L119" t="n">
-        <v>25644</v>
+        <v>25604</v>
       </c>
       <c r="M119" t="n">
-        <v>44877</v>
+        <v>44807</v>
       </c>
       <c r="N119" t="n">
-        <v>0.00012014</v>
+        <v>0.00039668</v>
       </c>
       <c r="O119" t="n">
-        <v>0.0002582</v>
+        <v>0.00060576</v>
       </c>
       <c r="P119" t="n">
-        <v>0.0002582</v>
+        <v>0.00060576</v>
       </c>
       <c r="Q119" t="n">
-        <v>4.7048e-06</v>
+        <v>1.4692e-05</v>
       </c>
       <c r="R119" t="n">
-        <v>6.8312e-06</v>
+        <v>1.7229e-05</v>
       </c>
       <c r="S119" t="n">
-        <v>1.1536e-05</v>
+        <v>3.1922e-05</v>
       </c>
       <c r="T119" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U119" t="n">
-        <v>3.757579803466797</v>
+        <v>3.740857124328613</v>
       </c>
     </row>
     <row r="120">
@@ -8704,46 +8704,46 @@
         <v>0.01</v>
       </c>
       <c r="H120" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I120" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>19233</v>
+        <v>19203</v>
       </c>
       <c r="L120" t="n">
-        <v>25644</v>
+        <v>25604</v>
       </c>
       <c r="M120" t="n">
-        <v>44877</v>
+        <v>44807</v>
       </c>
       <c r="N120" t="n">
-        <v>3.0667e-06</v>
+        <v>1.014e-05</v>
       </c>
       <c r="O120" t="n">
-        <v>6.7255e-06</v>
+        <v>1.6948e-05</v>
       </c>
       <c r="P120" t="n">
-        <v>6.7255e-06</v>
+        <v>1.6948e-05</v>
       </c>
       <c r="Q120" t="n">
-        <v>8.1905e-08</v>
+        <v>2.2784e-07</v>
       </c>
       <c r="R120" t="n">
-        <v>1.5722e-07</v>
+        <v>3.6857e-07</v>
       </c>
       <c r="S120" t="n">
-        <v>2.3913e-07</v>
+        <v>5.9641e-07</v>
       </c>
       <c r="T120" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U120" t="n">
-        <v>2.712863922119141</v>
+        <v>2.742856025695801</v>
       </c>
     </row>
     <row r="121">
@@ -8773,46 +8773,46 @@
         <v>0.01</v>
       </c>
       <c r="H121" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="I121" t="n">
-        <v>6411</v>
+        <v>6401</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>25644</v>
+        <v>25604</v>
       </c>
       <c r="L121" t="n">
-        <v>57699</v>
+        <v>57609</v>
       </c>
       <c r="M121" t="n">
-        <v>83343</v>
+        <v>83213</v>
       </c>
       <c r="N121" t="n">
-        <v>0.00019092</v>
+        <v>0.00019275</v>
       </c>
       <c r="O121" t="n">
-        <v>9.5345e-05</v>
+        <v>9.578599999999999e-05</v>
       </c>
       <c r="P121" t="n">
-        <v>0.00019092</v>
+        <v>0.00019275</v>
       </c>
       <c r="Q121" t="n">
-        <v>4.3317e-06</v>
+        <v>4.342e-06</v>
       </c>
       <c r="R121" t="n">
-        <v>2.1826e-06</v>
+        <v>2.2307e-06</v>
       </c>
       <c r="S121" t="n">
-        <v>6.5144e-06</v>
+        <v>6.5726e-06</v>
       </c>
       <c r="T121" t="n">
-        <v>0.0001559819060988925</v>
+        <v>0.0001562255897516013</v>
       </c>
       <c r="U121" t="n">
-        <v>3.401252031326294</v>
+        <v>3.434036016464233</v>
       </c>
     </row>
     <row r="122">
@@ -8842,46 +8842,46 @@
         <v>0.1</v>
       </c>
       <c r="H122" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I122" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>6390</v>
+        <v>6400</v>
       </c>
       <c r="L122" t="n">
-        <v>9585</v>
+        <v>9600</v>
       </c>
       <c r="M122" t="n">
-        <v>15975</v>
+        <v>16000</v>
       </c>
       <c r="N122" t="n">
-        <v>0.00026205</v>
+        <v>0.00032929</v>
       </c>
       <c r="O122" t="n">
-        <v>0.00026534</v>
+        <v>0.00033255</v>
       </c>
       <c r="P122" t="n">
-        <v>0.00026534</v>
+        <v>0.00033255</v>
       </c>
       <c r="Q122" t="n">
-        <v>6.3388e-05</v>
+        <v>7.969700000000001e-05</v>
       </c>
       <c r="R122" t="n">
-        <v>6.446100000000001e-05</v>
+        <v>8.076600000000001e-05</v>
       </c>
       <c r="S122" t="n">
-        <v>0.00012785</v>
+        <v>0.00016046</v>
       </c>
       <c r="T122" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U122" t="n">
-        <v>1.496606349945068</v>
+        <v>1.500869989395142</v>
       </c>
     </row>
     <row r="123">
@@ -8911,46 +8911,46 @@
         <v>0.1</v>
       </c>
       <c r="H123" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I123" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>9585</v>
+        <v>9600</v>
       </c>
       <c r="L123" t="n">
-        <v>12780</v>
+        <v>12800</v>
       </c>
       <c r="M123" t="n">
-        <v>22365</v>
+        <v>22400</v>
       </c>
       <c r="N123" t="n">
-        <v>3.1752e-06</v>
+        <v>3.2018e-06</v>
       </c>
       <c r="O123" t="n">
-        <v>1.6823e-06</v>
+        <v>1.7477e-06</v>
       </c>
       <c r="P123" t="n">
-        <v>3.1752e-06</v>
+        <v>3.2018e-06</v>
       </c>
       <c r="Q123" t="n">
-        <v>5.2427e-07</v>
+        <v>5.3781e-07</v>
       </c>
       <c r="R123" t="n">
-        <v>2.3471e-07</v>
+        <v>2.421e-07</v>
       </c>
       <c r="S123" t="n">
-        <v>7.5898e-07</v>
+        <v>7.7991e-07</v>
       </c>
       <c r="T123" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U123" t="n">
-        <v>1.812205076217651</v>
+        <v>1.819179058074951</v>
       </c>
     </row>
     <row r="124">
@@ -8980,46 +8980,46 @@
         <v>0.1</v>
       </c>
       <c r="H124" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I124" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>9585</v>
+        <v>9600</v>
       </c>
       <c r="L124" t="n">
-        <v>12780</v>
+        <v>12800</v>
       </c>
       <c r="M124" t="n">
-        <v>22365</v>
+        <v>22400</v>
       </c>
       <c r="N124" t="n">
-        <v>0.00013474</v>
+        <v>0.00015509</v>
       </c>
       <c r="O124" t="n">
-        <v>0.00013518</v>
+        <v>0.00015553</v>
       </c>
       <c r="P124" t="n">
-        <v>0.00013518</v>
+        <v>0.00015553</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.2682e-05</v>
+        <v>3.7623e-05</v>
       </c>
       <c r="R124" t="n">
-        <v>3.2825e-05</v>
+        <v>3.7766e-05</v>
       </c>
       <c r="S124" t="n">
-        <v>6.550699999999999e-05</v>
+        <v>7.5388e-05</v>
       </c>
       <c r="T124" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U124" t="n">
-        <v>1.924227237701416</v>
+        <v>1.892561197280884</v>
       </c>
     </row>
     <row r="125">
@@ -9049,46 +9049,46 @@
         <v>0.1</v>
       </c>
       <c r="H125" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I125" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>9585</v>
+        <v>9600</v>
       </c>
       <c r="L125" t="n">
-        <v>12780</v>
+        <v>12800</v>
       </c>
       <c r="M125" t="n">
-        <v>22365</v>
+        <v>22400</v>
       </c>
       <c r="N125" t="n">
-        <v>7.6456e-07</v>
+        <v>1.0601e-06</v>
       </c>
       <c r="O125" t="n">
-        <v>8.1751e-07</v>
+        <v>1.1271e-06</v>
       </c>
       <c r="P125" t="n">
-        <v>8.1751e-07</v>
+        <v>1.1271e-06</v>
       </c>
       <c r="Q125" t="n">
-        <v>1.1416e-07</v>
+        <v>1.5824e-07</v>
       </c>
       <c r="R125" t="n">
-        <v>1.1126e-07</v>
+        <v>1.5561e-07</v>
       </c>
       <c r="S125" t="n">
-        <v>2.2542e-07</v>
+        <v>3.1384e-07</v>
       </c>
       <c r="T125" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U125" t="n">
-        <v>1.788630962371826</v>
+        <v>1.797693967819214</v>
       </c>
     </row>
     <row r="126">
@@ -9118,46 +9118,46 @@
         <v>0.1</v>
       </c>
       <c r="H126" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I126" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>12780</v>
+        <v>12800</v>
       </c>
       <c r="L126" t="n">
-        <v>28755</v>
+        <v>28800</v>
       </c>
       <c r="M126" t="n">
-        <v>41535</v>
+        <v>41600</v>
       </c>
       <c r="N126" t="n">
-        <v>4.9126e-06</v>
+        <v>4.8694e-06</v>
       </c>
       <c r="O126" t="n">
-        <v>2.6577e-06</v>
+        <v>2.7391e-06</v>
       </c>
       <c r="P126" t="n">
-        <v>4.9126e-06</v>
+        <v>4.8694e-06</v>
       </c>
       <c r="Q126" t="n">
-        <v>7.5191e-07</v>
+        <v>7.6487e-07</v>
       </c>
       <c r="R126" t="n">
-        <v>3.6492e-07</v>
+        <v>3.8208e-07</v>
       </c>
       <c r="S126" t="n">
-        <v>1.1168e-06</v>
+        <v>1.147e-06</v>
       </c>
       <c r="T126" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U126" t="n">
-        <v>2.271785020828247</v>
+        <v>2.266301870346069</v>
       </c>
     </row>
     <row r="127">
@@ -9187,46 +9187,46 @@
         <v>0.05</v>
       </c>
       <c r="H127" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I127" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>6390</v>
+        <v>6400</v>
       </c>
       <c r="L127" t="n">
-        <v>9585</v>
+        <v>9600</v>
       </c>
       <c r="M127" t="n">
-        <v>15975</v>
+        <v>16000</v>
       </c>
       <c r="N127" t="n">
-        <v>0.00047628</v>
+        <v>0.00060365</v>
       </c>
       <c r="O127" t="n">
-        <v>0.00051508</v>
+        <v>0.00064264</v>
       </c>
       <c r="P127" t="n">
-        <v>0.00051508</v>
+        <v>0.00064264</v>
       </c>
       <c r="Q127" t="n">
-        <v>7.0384e-05</v>
+        <v>8.8877e-05</v>
       </c>
       <c r="R127" t="n">
-        <v>7.381300000000001e-05</v>
+        <v>9.2301e-05</v>
       </c>
       <c r="S127" t="n">
-        <v>0.0001442</v>
+        <v>0.00018118</v>
       </c>
       <c r="T127" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U127" t="n">
-        <v>1.488308906555176</v>
+        <v>1.493005037307739</v>
       </c>
     </row>
     <row r="128">
@@ -9256,46 +9256,46 @@
         <v>0.05</v>
       </c>
       <c r="H128" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I128" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>9585</v>
+        <v>9600</v>
       </c>
       <c r="L128" t="n">
-        <v>12780</v>
+        <v>12800</v>
       </c>
       <c r="M128" t="n">
-        <v>22365</v>
+        <v>22400</v>
       </c>
       <c r="N128" t="n">
-        <v>2.1395e-05</v>
+        <v>2.1243e-05</v>
       </c>
       <c r="O128" t="n">
-        <v>1.1486e-05</v>
+        <v>1.1699e-05</v>
       </c>
       <c r="P128" t="n">
-        <v>2.1395e-05</v>
+        <v>2.1243e-05</v>
       </c>
       <c r="Q128" t="n">
-        <v>1.8842e-06</v>
+        <v>1.9014e-06</v>
       </c>
       <c r="R128" t="n">
-        <v>8.9453e-07</v>
+        <v>8.9399e-07</v>
       </c>
       <c r="S128" t="n">
-        <v>2.7788e-06</v>
+        <v>2.7954e-06</v>
       </c>
       <c r="T128" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U128" t="n">
-        <v>1.793802976608276</v>
+        <v>1.795038938522339</v>
       </c>
     </row>
     <row r="129">
@@ -9325,46 +9325,46 @@
         <v>0.05</v>
       </c>
       <c r="H129" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I129" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>9585</v>
+        <v>9600</v>
       </c>
       <c r="L129" t="n">
-        <v>12780</v>
+        <v>12800</v>
       </c>
       <c r="M129" t="n">
-        <v>22365</v>
+        <v>22400</v>
       </c>
       <c r="N129" t="n">
-        <v>0.00025311</v>
+        <v>0.00029176</v>
       </c>
       <c r="O129" t="n">
-        <v>0.00025792</v>
+        <v>0.00029655</v>
       </c>
       <c r="P129" t="n">
-        <v>0.00025792</v>
+        <v>0.00029655</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.6856e-05</v>
+        <v>4.2452e-05</v>
       </c>
       <c r="R129" t="n">
-        <v>3.7263e-05</v>
+        <v>4.2858e-05</v>
       </c>
       <c r="S129" t="n">
-        <v>7.4118e-05</v>
+        <v>8.5311e-05</v>
       </c>
       <c r="T129" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U129" t="n">
-        <v>1.889203071594238</v>
+        <v>1.897300958633423</v>
       </c>
     </row>
     <row r="130">
@@ -9394,46 +9394,46 @@
         <v>0.05</v>
       </c>
       <c r="H130" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I130" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>9585</v>
+        <v>9600</v>
       </c>
       <c r="L130" t="n">
-        <v>12780</v>
+        <v>12800</v>
       </c>
       <c r="M130" t="n">
-        <v>22365</v>
+        <v>22400</v>
       </c>
       <c r="N130" t="n">
-        <v>2.9962e-06</v>
+        <v>4.2351e-06</v>
       </c>
       <c r="O130" t="n">
-        <v>3.1268e-06</v>
+        <v>4.3594e-06</v>
       </c>
       <c r="P130" t="n">
-        <v>3.1268e-06</v>
+        <v>4.3594e-06</v>
       </c>
       <c r="Q130" t="n">
-        <v>2.474e-07</v>
+        <v>3.4728e-07</v>
       </c>
       <c r="R130" t="n">
-        <v>2.524e-07</v>
+        <v>3.5256e-07</v>
       </c>
       <c r="S130" t="n">
-        <v>4.9979e-07</v>
+        <v>6.9983e-07</v>
       </c>
       <c r="T130" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U130" t="n">
-        <v>1.715908288955688</v>
+        <v>1.723500728607178</v>
       </c>
     </row>
     <row r="131">
@@ -9463,46 +9463,46 @@
         <v>0.05</v>
       </c>
       <c r="H131" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I131" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>12780</v>
+        <v>12800</v>
       </c>
       <c r="L131" t="n">
-        <v>28755</v>
+        <v>28800</v>
       </c>
       <c r="M131" t="n">
-        <v>41535</v>
+        <v>41600</v>
       </c>
       <c r="N131" t="n">
-        <v>3.3215e-05</v>
+        <v>3.2797e-05</v>
       </c>
       <c r="O131" t="n">
-        <v>1.791e-05</v>
+        <v>1.8335e-05</v>
       </c>
       <c r="P131" t="n">
-        <v>3.3215e-05</v>
+        <v>3.2797e-05</v>
       </c>
       <c r="Q131" t="n">
-        <v>2.7968e-06</v>
+        <v>2.8125e-06</v>
       </c>
       <c r="R131" t="n">
-        <v>1.3643e-06</v>
+        <v>1.3726e-06</v>
       </c>
       <c r="S131" t="n">
-        <v>4.1611e-06</v>
+        <v>4.1851e-06</v>
       </c>
       <c r="T131" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U131" t="n">
-        <v>2.20145583152771</v>
+        <v>2.338253021240234</v>
       </c>
     </row>
     <row r="132">
@@ -9532,46 +9532,46 @@
         <v>0.02</v>
       </c>
       <c r="H132" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I132" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>6390</v>
+        <v>6400</v>
       </c>
       <c r="L132" t="n">
-        <v>9585</v>
+        <v>9600</v>
       </c>
       <c r="M132" t="n">
-        <v>15975</v>
+        <v>16000</v>
       </c>
       <c r="N132" t="n">
-        <v>0.0008724200000000001</v>
+        <v>0.0011442</v>
       </c>
       <c r="O132" t="n">
-        <v>0.001467</v>
+        <v>0.0017727</v>
       </c>
       <c r="P132" t="n">
-        <v>0.001467</v>
+        <v>0.0017727</v>
       </c>
       <c r="Q132" t="n">
-        <v>6.3179e-05</v>
+        <v>8.2345e-05</v>
       </c>
       <c r="R132" t="n">
-        <v>8.2328e-05</v>
+        <v>0.00010146</v>
       </c>
       <c r="S132" t="n">
-        <v>0.00014551</v>
+        <v>0.0001838</v>
       </c>
       <c r="T132" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U132" t="n">
-        <v>1.490873098373413</v>
+        <v>1.499483823776245</v>
       </c>
     </row>
     <row r="133">
@@ -9601,46 +9601,46 @@
         <v>0.02</v>
       </c>
       <c r="H133" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I133" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>9585</v>
+        <v>9600</v>
       </c>
       <c r="L133" t="n">
-        <v>12780</v>
+        <v>12800</v>
       </c>
       <c r="M133" t="n">
-        <v>22365</v>
+        <v>22400</v>
       </c>
       <c r="N133" t="n">
-        <v>0.00029574</v>
+        <v>0.00029815</v>
       </c>
       <c r="O133" t="n">
-        <v>0.0001546</v>
+        <v>0.00015647</v>
       </c>
       <c r="P133" t="n">
-        <v>0.00029574</v>
+        <v>0.00029815</v>
       </c>
       <c r="Q133" t="n">
-        <v>1.0947e-05</v>
+        <v>1.0942e-05</v>
       </c>
       <c r="R133" t="n">
-        <v>5.419e-06</v>
+        <v>5.3982e-06</v>
       </c>
       <c r="S133" t="n">
-        <v>1.6366e-05</v>
+        <v>1.634e-05</v>
       </c>
       <c r="T133" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U133" t="n">
-        <v>1.799673795700073</v>
+        <v>1.802125930786133</v>
       </c>
     </row>
     <row r="134">
@@ -9670,46 +9670,46 @@
         <v>0.02</v>
       </c>
       <c r="H134" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I134" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>9585</v>
+        <v>9600</v>
       </c>
       <c r="L134" t="n">
-        <v>12780</v>
+        <v>12800</v>
       </c>
       <c r="M134" t="n">
-        <v>22365</v>
+        <v>22400</v>
       </c>
       <c r="N134" t="n">
-        <v>0.00056008</v>
+        <v>0.00065081</v>
       </c>
       <c r="O134" t="n">
-        <v>0.0006477399999999999</v>
+        <v>0.00074086</v>
       </c>
       <c r="P134" t="n">
-        <v>0.0006477399999999999</v>
+        <v>0.00074086</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.7109e-05</v>
+        <v>4.294e-05</v>
       </c>
       <c r="R134" t="n">
-        <v>3.944e-05</v>
+        <v>4.5265e-05</v>
       </c>
       <c r="S134" t="n">
-        <v>7.6549e-05</v>
+        <v>8.8206e-05</v>
       </c>
       <c r="T134" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U134" t="n">
-        <v>1.904457092285156</v>
+        <v>1.885726928710938</v>
       </c>
     </row>
     <row r="135">
@@ -9739,46 +9739,46 @@
         <v>0.02</v>
       </c>
       <c r="H135" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I135" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>9585</v>
+        <v>9600</v>
       </c>
       <c r="L135" t="n">
-        <v>12780</v>
+        <v>12800</v>
       </c>
       <c r="M135" t="n">
-        <v>22365</v>
+        <v>22400</v>
       </c>
       <c r="N135" t="n">
-        <v>1.4784e-05</v>
+        <v>2.2407e-05</v>
       </c>
       <c r="O135" t="n">
-        <v>2.0951e-05</v>
+        <v>2.8544e-05</v>
       </c>
       <c r="P135" t="n">
-        <v>2.0951e-05</v>
+        <v>2.8544e-05</v>
       </c>
       <c r="Q135" t="n">
-        <v>5.3657e-07</v>
+        <v>7.834599999999999e-07</v>
       </c>
       <c r="R135" t="n">
-        <v>6.6643e-07</v>
+        <v>9.1209e-07</v>
       </c>
       <c r="S135" t="n">
-        <v>1.203e-06</v>
+        <v>1.6955e-06</v>
       </c>
       <c r="T135" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U135" t="n">
-        <v>1.673412799835205</v>
+        <v>1.678473949432373</v>
       </c>
     </row>
     <row r="136">
@@ -9808,46 +9808,46 @@
         <v>0.02</v>
       </c>
       <c r="H136" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I136" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>12780</v>
+        <v>12800</v>
       </c>
       <c r="L136" t="n">
-        <v>28755</v>
+        <v>28800</v>
       </c>
       <c r="M136" t="n">
-        <v>41535</v>
+        <v>41600</v>
       </c>
       <c r="N136" t="n">
-        <v>0.00045361</v>
+        <v>0.00044968</v>
       </c>
       <c r="O136" t="n">
-        <v>0.00024096</v>
+        <v>0.00024317</v>
       </c>
       <c r="P136" t="n">
-        <v>0.00045361</v>
+        <v>0.00044968</v>
       </c>
       <c r="Q136" t="n">
-        <v>1.672e-05</v>
+        <v>1.6647e-05</v>
       </c>
       <c r="R136" t="n">
-        <v>8.314299999999999e-06</v>
+        <v>8.270100000000001e-06</v>
       </c>
       <c r="S136" t="n">
-        <v>2.5034e-05</v>
+        <v>2.4917e-05</v>
       </c>
       <c r="T136" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U136" t="n">
-        <v>2.162189960479736</v>
+        <v>2.161992073059082</v>
       </c>
     </row>
     <row r="137">
@@ -9877,46 +9877,46 @@
         <v>0.01</v>
       </c>
       <c r="H137" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I137" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>6390</v>
+        <v>6400</v>
       </c>
       <c r="L137" t="n">
-        <v>9585</v>
+        <v>9600</v>
       </c>
       <c r="M137" t="n">
-        <v>15975</v>
+        <v>16000</v>
       </c>
       <c r="N137" t="n">
-        <v>0.0029132</v>
+        <v>0.0030198</v>
       </c>
       <c r="O137" t="n">
-        <v>0.0048245</v>
+        <v>0.0054522</v>
       </c>
       <c r="P137" t="n">
-        <v>0.0048245</v>
+        <v>0.0054522</v>
       </c>
       <c r="Q137" t="n">
-        <v>0.00010027</v>
+        <v>0.00010145</v>
       </c>
       <c r="R137" t="n">
-        <v>0.00011895</v>
+        <v>0.00013663</v>
       </c>
       <c r="S137" t="n">
-        <v>0.00021922</v>
+        <v>0.00023808</v>
       </c>
       <c r="T137" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U137" t="n">
-        <v>1.495346069335938</v>
+        <v>1.498333930969238</v>
       </c>
     </row>
     <row r="138">
@@ -9946,46 +9946,46 @@
         <v>0.01</v>
       </c>
       <c r="H138" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I138" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>9585</v>
+        <v>9600</v>
       </c>
       <c r="L138" t="n">
-        <v>12780</v>
+        <v>12800</v>
       </c>
       <c r="M138" t="n">
-        <v>22365</v>
+        <v>22400</v>
       </c>
       <c r="N138" t="n">
-        <v>0.0021802</v>
+        <v>0.002175</v>
       </c>
       <c r="O138" t="n">
-        <v>0.0010903</v>
+        <v>0.0010865</v>
       </c>
       <c r="P138" t="n">
-        <v>0.0021802</v>
+        <v>0.002175</v>
       </c>
       <c r="Q138" t="n">
-        <v>4.9529e-05</v>
+        <v>4.9359e-05</v>
       </c>
       <c r="R138" t="n">
-        <v>2.4942e-05</v>
+        <v>2.4909e-05</v>
       </c>
       <c r="S138" t="n">
-        <v>7.4471e-05</v>
+        <v>7.4268e-05</v>
       </c>
       <c r="T138" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U138" t="n">
-        <v>1.793473958969116</v>
+        <v>1.816097021102905</v>
       </c>
     </row>
     <row r="139">
@@ -10015,46 +10015,46 @@
         <v>0.01</v>
       </c>
       <c r="H139" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I139" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>9585</v>
+        <v>9600</v>
       </c>
       <c r="L139" t="n">
-        <v>12780</v>
+        <v>12800</v>
       </c>
       <c r="M139" t="n">
-        <v>22365</v>
+        <v>22400</v>
       </c>
       <c r="N139" t="n">
-        <v>0.00081937</v>
+        <v>0.0009893899999999999</v>
       </c>
       <c r="O139" t="n">
-        <v>0.0015571</v>
+        <v>0.0017507</v>
       </c>
       <c r="P139" t="n">
-        <v>0.0015571</v>
+        <v>0.0017507</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.3882e-05</v>
+        <v>3.9466e-05</v>
       </c>
       <c r="R139" t="n">
-        <v>4.3017e-05</v>
+        <v>4.8809e-05</v>
       </c>
       <c r="S139" t="n">
-        <v>7.6899e-05</v>
+        <v>8.8275e-05</v>
       </c>
       <c r="T139" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U139" t="n">
-        <v>1.901907920837402</v>
+        <v>1.890565872192383</v>
       </c>
     </row>
     <row r="140">
@@ -10084,46 +10084,46 @@
         <v>0.01</v>
       </c>
       <c r="H140" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I140" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>9585</v>
+        <v>9600</v>
       </c>
       <c r="L140" t="n">
-        <v>12780</v>
+        <v>12800</v>
       </c>
       <c r="M140" t="n">
-        <v>22365</v>
+        <v>22400</v>
       </c>
       <c r="N140" t="n">
-        <v>2.7703e-05</v>
+        <v>4.5863e-05</v>
       </c>
       <c r="O140" t="n">
-        <v>8.289299999999999e-05</v>
+        <v>0.00010734</v>
       </c>
       <c r="P140" t="n">
-        <v>8.289299999999999e-05</v>
+        <v>0.00010734</v>
       </c>
       <c r="Q140" t="n">
-        <v>9.1732e-07</v>
+        <v>1.2673e-06</v>
       </c>
       <c r="R140" t="n">
-        <v>1.89e-06</v>
+        <v>2.4053e-06</v>
       </c>
       <c r="S140" t="n">
-        <v>2.8073e-06</v>
+        <v>3.6726e-06</v>
       </c>
       <c r="T140" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U140" t="n">
-        <v>1.663911819458008</v>
+        <v>1.666096925735474</v>
       </c>
     </row>
     <row r="141">
@@ -10153,46 +10153,46 @@
         <v>0.01</v>
       </c>
       <c r="H141" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="I141" t="n">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>12780</v>
+        <v>12800</v>
       </c>
       <c r="L141" t="n">
-        <v>28755</v>
+        <v>28800</v>
       </c>
       <c r="M141" t="n">
-        <v>41535</v>
+        <v>41600</v>
       </c>
       <c r="N141" t="n">
-        <v>0.003364</v>
+        <v>0.0033455</v>
       </c>
       <c r="O141" t="n">
-        <v>0.0016849</v>
+        <v>0.0016745</v>
       </c>
       <c r="P141" t="n">
-        <v>0.003364</v>
+        <v>0.0033455</v>
       </c>
       <c r="Q141" t="n">
-        <v>7.666299999999999e-05</v>
+        <v>7.6154e-05</v>
       </c>
       <c r="R141" t="n">
-        <v>3.8666e-05</v>
+        <v>3.8504e-05</v>
       </c>
       <c r="S141" t="n">
-        <v>0.00011533</v>
+        <v>0.00011466</v>
       </c>
       <c r="T141" t="n">
-        <v>0.0003129890453834116</v>
+        <v>0.0003125</v>
       </c>
       <c r="U141" t="n">
-        <v>2.146192073822021</v>
+        <v>2.153793096542358</v>
       </c>
     </row>
     <row r="142">
@@ -10261,7 +10261,7 @@
         <v>0.000625</v>
       </c>
       <c r="U142" t="n">
-        <v>0.7634937763214111</v>
+        <v>0.7669317722320557</v>
       </c>
     </row>
     <row r="143">
@@ -10330,7 +10330,7 @@
         <v>0.000625</v>
       </c>
       <c r="U143" t="n">
-        <v>0.9466102123260498</v>
+        <v>0.9614830017089844</v>
       </c>
     </row>
     <row r="144">
@@ -10399,7 +10399,7 @@
         <v>0.000625</v>
       </c>
       <c r="U144" t="n">
-        <v>0.9638636112213135</v>
+        <v>0.9636259078979492</v>
       </c>
     </row>
     <row r="145">
@@ -10468,7 +10468,7 @@
         <v>0.000625</v>
       </c>
       <c r="U145" t="n">
-        <v>0.9477279186248779</v>
+        <v>0.9501869678497314</v>
       </c>
     </row>
     <row r="146">
@@ -10537,7 +10537,7 @@
         <v>0.000625</v>
       </c>
       <c r="U146" t="n">
-        <v>1.198469877243042</v>
+        <v>1.2033851146698</v>
       </c>
     </row>
     <row r="147">
@@ -10606,7 +10606,7 @@
         <v>0.000625</v>
       </c>
       <c r="U147" t="n">
-        <v>0.7661728858947754</v>
+        <v>0.7691688537597656</v>
       </c>
     </row>
     <row r="148">
@@ -10675,7 +10675,7 @@
         <v>0.000625</v>
       </c>
       <c r="U148" t="n">
-        <v>0.9442832469940186</v>
+        <v>0.9385120868682861</v>
       </c>
     </row>
     <row r="149">
@@ -10744,7 +10744,7 @@
         <v>0.000625</v>
       </c>
       <c r="U149" t="n">
-        <v>0.9715299606323242</v>
+        <v>0.9628872871398926</v>
       </c>
     </row>
     <row r="150">
@@ -10813,7 +10813,7 @@
         <v>0.000625</v>
       </c>
       <c r="U150" t="n">
-        <v>0.9505589008331299</v>
+        <v>0.95182204246521</v>
       </c>
     </row>
     <row r="151">
@@ -10882,7 +10882,7 @@
         <v>0.000625</v>
       </c>
       <c r="U151" t="n">
-        <v>1.195195913314819</v>
+        <v>1.199440956115723</v>
       </c>
     </row>
     <row r="152">
@@ -10951,7 +10951,7 @@
         <v>0.000625</v>
       </c>
       <c r="U152" t="n">
-        <v>0.7662651538848877</v>
+        <v>0.76198410987854</v>
       </c>
     </row>
     <row r="153">
@@ -11020,7 +11020,7 @@
         <v>0.000625</v>
       </c>
       <c r="U153" t="n">
-        <v>0.9428119659423828</v>
+        <v>0.9358589649200439</v>
       </c>
     </row>
     <row r="154">
@@ -11089,7 +11089,7 @@
         <v>0.000625</v>
       </c>
       <c r="U154" t="n">
-        <v>0.9621829986572266</v>
+        <v>0.9664130210876465</v>
       </c>
     </row>
     <row r="155">
@@ -11158,7 +11158,7 @@
         <v>0.000625</v>
       </c>
       <c r="U155" t="n">
-        <v>0.9479451179504395</v>
+        <v>0.9426639080047607</v>
       </c>
     </row>
     <row r="156">
@@ -11227,7 +11227,7 @@
         <v>0.000625</v>
       </c>
       <c r="U156" t="n">
-        <v>1.196312189102173</v>
+        <v>1.19425106048584</v>
       </c>
     </row>
     <row r="157">
@@ -11296,7 +11296,7 @@
         <v>0.000625</v>
       </c>
       <c r="U157" t="n">
-        <v>0.7629289627075195</v>
+        <v>0.7692091464996338</v>
       </c>
     </row>
     <row r="158">
@@ -11365,7 +11365,7 @@
         <v>0.000625</v>
       </c>
       <c r="U158" t="n">
-        <v>0.9404113292694092</v>
+        <v>0.940375804901123</v>
       </c>
     </row>
     <row r="159">
@@ -11434,7 +11434,7 @@
         <v>0.000625</v>
       </c>
       <c r="U159" t="n">
-        <v>0.9674229621887207</v>
+        <v>0.9702668190002441</v>
       </c>
     </row>
     <row r="160">
@@ -11503,7 +11503,7 @@
         <v>0.000625</v>
       </c>
       <c r="U160" t="n">
-        <v>0.9499409198760986</v>
+        <v>0.9467897415161133</v>
       </c>
     </row>
     <row r="161">
@@ -11572,7 +11572,7 @@
         <v>0.000625</v>
       </c>
       <c r="U161" t="n">
-        <v>1.200538873672485</v>
+        <v>1.194885730743408</v>
       </c>
     </row>
     <row r="162">
@@ -11641,7 +11641,7 @@
         <v>0.00125</v>
       </c>
       <c r="U162" t="n">
-        <v>0.4018378257751465</v>
+        <v>0.4043869972229004</v>
       </c>
     </row>
     <row r="163">
@@ -11710,7 +11710,7 @@
         <v>0.00125</v>
       </c>
       <c r="U163" t="n">
-        <v>0.501126766204834</v>
+        <v>0.4934141635894775</v>
       </c>
     </row>
     <row r="164">
@@ -11779,7 +11779,7 @@
         <v>0.00125</v>
       </c>
       <c r="U164" t="n">
-        <v>0.5050868988037109</v>
+        <v>0.5090360641479492</v>
       </c>
     </row>
     <row r="165">
@@ -11848,7 +11848,7 @@
         <v>0.00125</v>
       </c>
       <c r="U165" t="n">
-        <v>0.5017251968383789</v>
+        <v>0.5037271976470947</v>
       </c>
     </row>
     <row r="166">
@@ -11917,7 +11917,7 @@
         <v>0.002024291497975709</v>
       </c>
       <c r="U166" t="n">
-        <v>0.6403100490570068</v>
+        <v>0.6451060771942139</v>
       </c>
     </row>
     <row r="167">
@@ -11986,7 +11986,7 @@
         <v>0.00125</v>
       </c>
       <c r="U167" t="n">
-        <v>0.4035739898681641</v>
+        <v>0.4066240787506104</v>
       </c>
     </row>
     <row r="168">
@@ -12055,7 +12055,7 @@
         <v>0.00125</v>
       </c>
       <c r="U168" t="n">
-        <v>0.495952844619751</v>
+        <v>0.4974789619445801</v>
       </c>
     </row>
     <row r="169">
@@ -12124,7 +12124,7 @@
         <v>0.00125</v>
       </c>
       <c r="U169" t="n">
-        <v>0.5047919750213623</v>
+        <v>0.5067780017852783</v>
       </c>
     </row>
     <row r="170">
@@ -12193,7 +12193,7 @@
         <v>0.00125</v>
       </c>
       <c r="U170" t="n">
-        <v>0.5145149230957031</v>
+        <v>0.5003330707550049</v>
       </c>
     </row>
     <row r="171">
@@ -12262,7 +12262,7 @@
         <v>0.002024291497975709</v>
       </c>
       <c r="U171" t="n">
-        <v>0.6433000564575195</v>
+        <v>0.6418402194976807</v>
       </c>
     </row>
     <row r="172">
@@ -12331,7 +12331,7 @@
         <v>0.00125</v>
       </c>
       <c r="U172" t="n">
-        <v>0.4064450263977051</v>
+        <v>0.4183211326599121</v>
       </c>
     </row>
     <row r="173">
@@ -12400,7 +12400,7 @@
         <v>0.00125</v>
       </c>
       <c r="U173" t="n">
-        <v>0.4945540428161621</v>
+        <v>0.4932510852813721</v>
       </c>
     </row>
     <row r="174">
@@ -12469,7 +12469,7 @@
         <v>0.00125</v>
       </c>
       <c r="U174" t="n">
-        <v>0.5046257972717285</v>
+        <v>0.5003352165222168</v>
       </c>
     </row>
     <row r="175">
@@ -12538,7 +12538,7 @@
         <v>0.00125</v>
       </c>
       <c r="U175" t="n">
-        <v>0.5013589859008789</v>
+        <v>0.5041980743408203</v>
       </c>
     </row>
     <row r="176">
@@ -12607,7 +12607,7 @@
         <v>0.002024291497975709</v>
       </c>
       <c r="U176" t="n">
-        <v>0.6488089561462402</v>
+        <v>0.6443710327148438</v>
       </c>
     </row>
     <row r="177">
@@ -12676,7 +12676,7 @@
         <v>0.00125</v>
       </c>
       <c r="U177" t="n">
-        <v>0.40618896484375</v>
+        <v>0.4017610549926758</v>
       </c>
     </row>
     <row r="178">
@@ -12745,7 +12745,7 @@
         <v>0.00125</v>
       </c>
       <c r="U178" t="n">
-        <v>0.4988322257995605</v>
+        <v>0.4901809692382812</v>
       </c>
     </row>
     <row r="179">
@@ -12814,7 +12814,7 @@
         <v>0.00125</v>
       </c>
       <c r="U179" t="n">
-        <v>0.5169360637664795</v>
+        <v>0.5061168670654297</v>
       </c>
     </row>
     <row r="180">
@@ -12883,7 +12883,7 @@
         <v>0.00125</v>
       </c>
       <c r="U180" t="n">
-        <v>0.499791145324707</v>
+        <v>0.503687858581543</v>
       </c>
     </row>
     <row r="181">
@@ -12952,7 +12952,7 @@
         <v>0.002024291497975709</v>
       </c>
       <c r="U181" t="n">
-        <v>0.6444871425628662</v>
+        <v>0.6477508544921875</v>
       </c>
     </row>
     <row r="182">
@@ -13021,7 +13021,7 @@
         <v>0.0025</v>
       </c>
       <c r="U182" t="n">
-        <v>0.2213461399078369</v>
+        <v>0.220632791519165</v>
       </c>
     </row>
     <row r="183">
@@ -13090,7 +13090,7 @@
         <v>0.0025</v>
       </c>
       <c r="U183" t="n">
-        <v>0.2683260440826416</v>
+        <v>0.2699830532073975</v>
       </c>
     </row>
     <row r="184">
@@ -13159,7 +13159,7 @@
         <v>0.0025</v>
       </c>
       <c r="U184" t="n">
-        <v>0.2734999656677246</v>
+        <v>0.2720808982849121</v>
       </c>
     </row>
     <row r="185">
@@ -13228,7 +13228,7 @@
         <v>0.0025</v>
       </c>
       <c r="U185" t="n">
-        <v>0.2722780704498291</v>
+        <v>0.2670037746429443</v>
       </c>
     </row>
     <row r="186">
@@ -13297,7 +13297,7 @@
         <v>0.004098360655737705</v>
       </c>
       <c r="U186" t="n">
-        <v>0.4220890998840332</v>
+        <v>0.4226081371307373</v>
       </c>
     </row>
     <row r="187">
@@ -13366,7 +13366,7 @@
         <v>0.0025</v>
       </c>
       <c r="U187" t="n">
-        <v>0.2181158065795898</v>
+        <v>0.2185559272766113</v>
       </c>
     </row>
     <row r="188">
@@ -13435,7 +13435,7 @@
         <v>0.0025</v>
       </c>
       <c r="U188" t="n">
-        <v>0.2697179317474365</v>
+        <v>0.2654809951782227</v>
       </c>
     </row>
     <row r="189">
@@ -13504,7 +13504,7 @@
         <v>0.0025</v>
       </c>
       <c r="U189" t="n">
-        <v>0.2705600261688232</v>
+        <v>0.26971435546875</v>
       </c>
     </row>
     <row r="190">
@@ -13573,7 +13573,7 @@
         <v>0.0025</v>
       </c>
       <c r="U190" t="n">
-        <v>0.26934814453125</v>
+        <v>0.2703990936279297</v>
       </c>
     </row>
     <row r="191">
@@ -13642,7 +13642,7 @@
         <v>0.004098360655737705</v>
       </c>
       <c r="U191" t="n">
-        <v>0.4220218658447266</v>
+        <v>0.4185709953308105</v>
       </c>
     </row>
     <row r="192">
@@ -13711,7 +13711,7 @@
         <v>0.0025</v>
       </c>
       <c r="U192" t="n">
-        <v>0.2168710231781006</v>
+        <v>0.2222251892089844</v>
       </c>
     </row>
     <row r="193">
@@ -13780,7 +13780,7 @@
         <v>0.0025</v>
       </c>
       <c r="U193" t="n">
-        <v>0.2644557952880859</v>
+        <v>0.2670283317565918</v>
       </c>
     </row>
     <row r="194">
@@ -13849,7 +13849,7 @@
         <v>0.0025</v>
       </c>
       <c r="U194" t="n">
-        <v>0.2691559791564941</v>
+        <v>0.273622989654541</v>
       </c>
     </row>
     <row r="195">
@@ -13918,7 +13918,7 @@
         <v>0.0025</v>
       </c>
       <c r="U195" t="n">
-        <v>0.2696402072906494</v>
+        <v>0.2716422080993652</v>
       </c>
     </row>
     <row r="196">
@@ -13987,7 +13987,7 @@
         <v>0.004098360655737705</v>
       </c>
       <c r="U196" t="n">
-        <v>0.4196810722351074</v>
+        <v>0.4264578819274902</v>
       </c>
     </row>
     <row r="197">
@@ -14056,7 +14056,7 @@
         <v>0.0025</v>
       </c>
       <c r="U197" t="n">
-        <v>0.2177212238311768</v>
+        <v>0.2206110954284668</v>
       </c>
     </row>
     <row r="198">
@@ -14125,7 +14125,7 @@
         <v>0.0025</v>
       </c>
       <c r="U198" t="n">
-        <v>0.2649819850921631</v>
+        <v>0.2642068862915039</v>
       </c>
     </row>
     <row r="199">
@@ -14194,7 +14194,7 @@
         <v>0.0025</v>
       </c>
       <c r="U199" t="n">
-        <v>0.2721118927001953</v>
+        <v>0.2670547962188721</v>
       </c>
     </row>
     <row r="200">
@@ -14263,7 +14263,7 @@
         <v>0.0025</v>
       </c>
       <c r="U200" t="n">
-        <v>0.2704977989196777</v>
+        <v>0.2715508937835693</v>
       </c>
     </row>
     <row r="201">
@@ -14332,7 +14332,7 @@
         <v>0.004098360655737705</v>
       </c>
       <c r="U201" t="n">
-        <v>0.4190840721130371</v>
+        <v>0.4417910575866699</v>
       </c>
     </row>
     <row r="202">
@@ -14401,7 +14401,7 @@
         <v>0.005</v>
       </c>
       <c r="U202" t="n">
-        <v>0.1336519718170166</v>
+        <v>0.1354870796203613</v>
       </c>
     </row>
     <row r="203">
@@ -14470,7 +14470,7 @@
         <v>0.005</v>
       </c>
       <c r="U203" t="n">
-        <v>0.1573948860168457</v>
+        <v>0.1583080291748047</v>
       </c>
     </row>
     <row r="204">
@@ -14539,7 +14539,7 @@
         <v>0.005</v>
       </c>
       <c r="U204" t="n">
-        <v>0.1567122936248779</v>
+        <v>0.1538550853729248</v>
       </c>
     </row>
     <row r="205">
@@ -14608,7 +14608,7 @@
         <v>0.005</v>
       </c>
       <c r="U205" t="n">
-        <v>0.1558408737182617</v>
+        <v>0.1570532321929932</v>
       </c>
     </row>
     <row r="206">
@@ -14677,7 +14677,7 @@
         <v>0.006289308176100629</v>
       </c>
       <c r="U206" t="n">
-        <v>0.3486247062683105</v>
+        <v>0.3473629951477051</v>
       </c>
     </row>
     <row r="207">
@@ -14746,7 +14746,7 @@
         <v>0.005</v>
       </c>
       <c r="U207" t="n">
-        <v>0.134713888168335</v>
+        <v>0.1354460716247559</v>
       </c>
     </row>
     <row r="208">
@@ -14815,7 +14815,7 @@
         <v>0.005</v>
       </c>
       <c r="U208" t="n">
-        <v>0.1584649085998535</v>
+        <v>0.1595902442932129</v>
       </c>
     </row>
     <row r="209">
@@ -14884,7 +14884,7 @@
         <v>0.005</v>
       </c>
       <c r="U209" t="n">
-        <v>0.157069206237793</v>
+        <v>0.1528220176696777</v>
       </c>
     </row>
     <row r="210">
@@ -14953,7 +14953,7 @@
         <v>0.005</v>
       </c>
       <c r="U210" t="n">
-        <v>0.156926155090332</v>
+        <v>0.1573359966278076</v>
       </c>
     </row>
     <row r="211">
@@ -15022,7 +15022,7 @@
         <v>0.006289308176100629</v>
       </c>
       <c r="U211" t="n">
-        <v>0.3429319858551025</v>
+        <v>0.3468449115753174</v>
       </c>
     </row>
     <row r="212">
@@ -15091,7 +15091,7 @@
         <v>0.005</v>
       </c>
       <c r="U212" t="n">
-        <v>0.136059045791626</v>
+        <v>0.1345069408416748</v>
       </c>
     </row>
     <row r="213">
@@ -15160,7 +15160,7 @@
         <v>0.005</v>
       </c>
       <c r="U213" t="n">
-        <v>0.1595537662506104</v>
+        <v>0.1589171886444092</v>
       </c>
     </row>
     <row r="214">
@@ -15229,7 +15229,7 @@
         <v>0.005</v>
       </c>
       <c r="U214" t="n">
-        <v>0.1576638221740723</v>
+        <v>0.1526458263397217</v>
       </c>
     </row>
     <row r="215">
@@ -15298,7 +15298,7 @@
         <v>0.005</v>
       </c>
       <c r="U215" t="n">
-        <v>0.1556632518768311</v>
+        <v>0.1605050563812256</v>
       </c>
     </row>
     <row r="216">
@@ -15367,7 +15367,7 @@
         <v>0.006289308176100629</v>
       </c>
       <c r="U216" t="n">
-        <v>0.3462419509887695</v>
+        <v>0.3444809913635254</v>
       </c>
     </row>
     <row r="217">
@@ -15436,7 +15436,7 @@
         <v>0.005</v>
       </c>
       <c r="U217" t="n">
-        <v>0.134030818939209</v>
+        <v>0.1331729888916016</v>
       </c>
     </row>
     <row r="218">
@@ -15505,7 +15505,7 @@
         <v>0.005</v>
       </c>
       <c r="U218" t="n">
-        <v>0.1549952030181885</v>
+        <v>0.1587560176849365</v>
       </c>
     </row>
     <row r="219">
@@ -15574,7 +15574,7 @@
         <v>0.005</v>
       </c>
       <c r="U219" t="n">
-        <v>0.1559090614318848</v>
+        <v>0.153688907623291</v>
       </c>
     </row>
     <row r="220">
@@ -15643,7 +15643,7 @@
         <v>0.005</v>
       </c>
       <c r="U220" t="n">
-        <v>0.1577322483062744</v>
+        <v>0.1551079750061035</v>
       </c>
     </row>
     <row r="221">
@@ -15712,7 +15712,7 @@
         <v>0.006289308176100629</v>
       </c>
       <c r="U221" t="n">
-        <v>0.348182201385498</v>
+        <v>0.3489010334014893</v>
       </c>
     </row>
     <row r="222">
@@ -15781,7 +15781,7 @@
         <v>0.01</v>
       </c>
       <c r="U222" t="n">
-        <v>0.08829593658447266</v>
+        <v>0.08764290809631348</v>
       </c>
     </row>
     <row r="223">
@@ -15850,7 +15850,7 @@
         <v>0.01</v>
       </c>
       <c r="U223" t="n">
-        <v>0.09866690635681152</v>
+        <v>0.1022846698760986</v>
       </c>
     </row>
     <row r="224">
@@ -15919,7 +15919,7 @@
         <v>0.01</v>
       </c>
       <c r="U224" t="n">
-        <v>0.09909296035766602</v>
+        <v>0.0980679988861084</v>
       </c>
     </row>
     <row r="225">
@@ -15988,7 +15988,7 @@
         <v>0.01</v>
       </c>
       <c r="U225" t="n">
-        <v>0.103076696395874</v>
+        <v>0.101466178894043</v>
       </c>
     </row>
     <row r="226">
@@ -16057,7 +16057,7 @@
         <v>0.01</v>
       </c>
       <c r="U226" t="n">
-        <v>0.124284029006958</v>
+        <v>0.1241459846496582</v>
       </c>
     </row>
     <row r="227">
@@ -16126,7 +16126,7 @@
         <v>0.01</v>
       </c>
       <c r="U227" t="n">
-        <v>0.08761119842529297</v>
+        <v>0.08598494529724121</v>
       </c>
     </row>
     <row r="228">
@@ -16195,7 +16195,7 @@
         <v>0.01</v>
       </c>
       <c r="U228" t="n">
-        <v>0.1006309986114502</v>
+        <v>0.09933900833129883</v>
       </c>
     </row>
     <row r="229">
@@ -16264,7 +16264,7 @@
         <v>0.01</v>
       </c>
       <c r="U229" t="n">
-        <v>0.1005167961120605</v>
+        <v>0.1005399227142334</v>
       </c>
     </row>
     <row r="230">
@@ -16333,7 +16333,7 @@
         <v>0.01</v>
       </c>
       <c r="U230" t="n">
-        <v>0.1011240482330322</v>
+        <v>0.1003801822662354</v>
       </c>
     </row>
     <row r="231">
@@ -16402,7 +16402,7 @@
         <v>0.01</v>
       </c>
       <c r="U231" t="n">
-        <v>0.1269698143005371</v>
+        <v>0.1273972988128662</v>
       </c>
     </row>
     <row r="232">
@@ -16471,7 +16471,7 @@
         <v>0.01</v>
       </c>
       <c r="U232" t="n">
-        <v>0.0865483283996582</v>
+        <v>0.08609318733215332</v>
       </c>
     </row>
     <row r="233">
@@ -16540,7 +16540,7 @@
         <v>0.01</v>
       </c>
       <c r="U233" t="n">
-        <v>0.1010768413543701</v>
+        <v>0.1010761260986328</v>
       </c>
     </row>
     <row r="234">
@@ -16609,7 +16609,7 @@
         <v>0.01</v>
       </c>
       <c r="U234" t="n">
-        <v>0.1004631519317627</v>
+        <v>0.1019058227539062</v>
       </c>
     </row>
     <row r="235">
@@ -16678,7 +16678,7 @@
         <v>0.01</v>
       </c>
       <c r="U235" t="n">
-        <v>0.101478099822998</v>
+        <v>0.09950399398803711</v>
       </c>
     </row>
     <row r="236">
@@ -16747,7 +16747,7 @@
         <v>0.01</v>
       </c>
       <c r="U236" t="n">
-        <v>0.126615047454834</v>
+        <v>0.1270692348480225</v>
       </c>
     </row>
     <row r="237">
@@ -16816,7 +16816,7 @@
         <v>0.01</v>
       </c>
       <c r="U237" t="n">
-        <v>0.08805704116821289</v>
+        <v>0.08523797988891602</v>
       </c>
     </row>
     <row r="238">
@@ -16885,7 +16885,7 @@
         <v>0.01</v>
       </c>
       <c r="U238" t="n">
-        <v>0.1019740104675293</v>
+        <v>0.1000282764434814</v>
       </c>
     </row>
     <row r="239">
@@ -16954,7 +16954,7 @@
         <v>0.01</v>
       </c>
       <c r="U239" t="n">
-        <v>0.0998079776763916</v>
+        <v>0.1006209850311279</v>
       </c>
     </row>
     <row r="240">
@@ -17023,7 +17023,7 @@
         <v>0.01</v>
       </c>
       <c r="U240" t="n">
-        <v>0.1024320125579834</v>
+        <v>0.09885573387145996</v>
       </c>
     </row>
     <row r="241">
@@ -17092,7 +17092,7 @@
         <v>0.01</v>
       </c>
       <c r="U241" t="n">
-        <v>0.1257781982421875</v>
+        <v>0.1275157928466797</v>
       </c>
     </row>
   </sheetData>
